--- a/docs/forms/форма-10.2.xlsx
+++ b/docs/forms/форма-10.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86144497-1D3B-4629-9DF3-9C57719674EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27375" windowHeight="10980"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Форма № 10.2 демонтаж КЛ" sheetId="6" r:id="rId1"/>
@@ -12,12 +13,17 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Форма № 10.2 демонтаж КЛ'!$A$1:$AI$65</definedName>
   </definedNames>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="133">
   <si>
     <t>Ф.И.О. указывать полностью</t>
   </si>
@@ -441,8 +447,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="28" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,6 +646,14 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -1467,13 +1481,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1797,9 +1814,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1862,7 +1876,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Овал 1"/>
+        <xdr:cNvPr id="2" name="Овал 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1988,6 +2008,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2023,6 +2060,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2198,7 +2252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:AX72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2216,43 +2270,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
-      <c r="AC1" s="99"/>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="99"/>
-      <c r="AG1" s="99"/>
-      <c r="AH1" s="99"/>
-      <c r="AI1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="100"/>
+      <c r="V1" s="100"/>
+      <c r="W1" s="100"/>
+      <c r="X1" s="100"/>
+      <c r="Y1" s="100"/>
+      <c r="Z1" s="100"/>
+      <c r="AA1" s="100"/>
+      <c r="AB1" s="100"/>
+      <c r="AC1" s="100"/>
+      <c r="AD1" s="100"/>
+      <c r="AE1" s="100"/>
+      <c r="AF1" s="100"/>
+      <c r="AG1" s="100"/>
+      <c r="AH1" s="100"/>
+      <c r="AI1" s="100"/>
       <c r="AJ1" s="87"/>
       <c r="AK1" s="87"/>
       <c r="AL1" s="87"/>
@@ -2265,43 +2319,43 @@
       <c r="AS1" s="87"/>
     </row>
     <row r="2" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="101" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
-      <c r="Z2" s="100"/>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="100"/>
-      <c r="AD2" s="100"/>
-      <c r="AE2" s="100"/>
-      <c r="AF2" s="100"/>
-      <c r="AG2" s="100"/>
-      <c r="AH2" s="100"/>
-      <c r="AI2" s="100"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
+      <c r="T2" s="101"/>
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
+      <c r="X2" s="101"/>
+      <c r="Y2" s="101"/>
+      <c r="Z2" s="101"/>
+      <c r="AA2" s="101"/>
+      <c r="AB2" s="101"/>
+      <c r="AC2" s="101"/>
+      <c r="AD2" s="101"/>
+      <c r="AE2" s="101"/>
+      <c r="AF2" s="101"/>
+      <c r="AG2" s="101"/>
+      <c r="AH2" s="101"/>
+      <c r="AI2" s="101"/>
       <c r="AJ2" s="87"/>
       <c r="AK2" s="87"/>
       <c r="AL2" s="87"/>
@@ -2313,42 +2367,42 @@
       <c r="AR2" s="87"/>
       <c r="AS2" s="87"/>
     </row>
-    <row r="3" spans="1:50" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="101"/>
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101"/>
-      <c r="U3" s="101"/>
-      <c r="V3" s="101"/>
-      <c r="W3" s="101"/>
-      <c r="X3" s="101"/>
-      <c r="Y3" s="101"/>
-      <c r="Z3" s="101"/>
-      <c r="AA3" s="101"/>
-      <c r="AB3" s="101"/>
-      <c r="AC3" s="101"/>
-      <c r="AD3" s="101"/>
-      <c r="AE3" s="101"/>
-      <c r="AF3" s="101"/>
-      <c r="AG3" s="101"/>
-      <c r="AH3" s="101"/>
-      <c r="AI3" s="101"/>
+    <row r="3" spans="1:50" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="102"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="102"/>
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="102"/>
       <c r="AJ3" s="87"/>
       <c r="AK3" s="87"/>
       <c r="AL3" s="87"/>
@@ -2416,33 +2470,33 @@
       <c r="A5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="107"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="107"/>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="107"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="102" t="s">
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="109"/>
+      <c r="W5" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="X5" s="102"/>
+      <c r="X5" s="103"/>
       <c r="Y5" s="65"/>
       <c r="Z5" s="65"/>
       <c r="AA5" s="65"/>
@@ -2491,21 +2545,21 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="103" t="s">
+      <c r="J6" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="104"/>
+      <c r="T6" s="104"/>
+      <c r="U6" s="104"/>
+      <c r="V6" s="104"/>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
@@ -2548,10 +2602,10 @@
     </row>
     <row r="7" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="120"/>
+      <c r="C7" s="121"/>
       <c r="D7" s="66"/>
       <c r="E7" s="66"/>
       <c r="F7" s="65"/>
@@ -2565,10 +2619,10 @@
       <c r="N7" s="66"/>
       <c r="O7" s="66"/>
       <c r="P7" s="66"/>
-      <c r="Q7" s="121" t="s">
+      <c r="Q7" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="R7" s="121"/>
+      <c r="R7" s="122"/>
       <c r="S7" s="66"/>
       <c r="T7" s="71"/>
       <c r="U7" s="72"/>
@@ -2738,41 +2792,41 @@
       <c r="A10" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="123" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="124"/>
-      <c r="X10" s="124"/>
-      <c r="Y10" s="124"/>
-      <c r="Z10" s="124"/>
-      <c r="AA10" s="124"/>
-      <c r="AB10" s="124"/>
-      <c r="AC10" s="124"/>
-      <c r="AD10" s="124"/>
-      <c r="AE10" s="124"/>
-      <c r="AF10" s="124"/>
-      <c r="AG10" s="124"/>
-      <c r="AH10" s="125"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="124"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="125"/>
+      <c r="Q10" s="125"/>
+      <c r="R10" s="125"/>
+      <c r="S10" s="125"/>
+      <c r="T10" s="125"/>
+      <c r="U10" s="125"/>
+      <c r="V10" s="125"/>
+      <c r="W10" s="125"/>
+      <c r="X10" s="125"/>
+      <c r="Y10" s="125"/>
+      <c r="Z10" s="125"/>
+      <c r="AA10" s="125"/>
+      <c r="AB10" s="125"/>
+      <c r="AC10" s="125"/>
+      <c r="AD10" s="125"/>
+      <c r="AE10" s="125"/>
+      <c r="AF10" s="125"/>
+      <c r="AG10" s="125"/>
+      <c r="AH10" s="126"/>
       <c r="AI10" s="25"/>
       <c r="AJ10" s="87"/>
       <c r="AK10" s="87"/>
@@ -2799,30 +2853,30 @@
     </row>
     <row r="11" spans="1:50" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
-      <c r="M11" s="129" t="s">
+      <c r="M11" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="N11" s="129"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="129"/>
-      <c r="R11" s="129"/>
-      <c r="S11" s="129"/>
-      <c r="T11" s="129"/>
-      <c r="U11" s="129"/>
-      <c r="V11" s="129"/>
-      <c r="W11" s="129"/>
-      <c r="X11" s="129"/>
-      <c r="Y11" s="129"/>
-      <c r="Z11" s="129"/>
-      <c r="AA11" s="129"/>
-      <c r="AB11" s="129"/>
-      <c r="AC11" s="129"/>
-      <c r="AD11" s="129"/>
-      <c r="AE11" s="129"/>
-      <c r="AF11" s="129"/>
-      <c r="AG11" s="129"/>
-      <c r="AH11" s="129"/>
+      <c r="N11" s="130"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="130"/>
+      <c r="R11" s="130"/>
+      <c r="S11" s="130"/>
+      <c r="T11" s="130"/>
+      <c r="U11" s="130"/>
+      <c r="V11" s="130"/>
+      <c r="W11" s="130"/>
+      <c r="X11" s="130"/>
+      <c r="Y11" s="130"/>
+      <c r="Z11" s="130"/>
+      <c r="AA11" s="130"/>
+      <c r="AB11" s="130"/>
+      <c r="AC11" s="130"/>
+      <c r="AD11" s="130"/>
+      <c r="AE11" s="130"/>
+      <c r="AF11" s="130"/>
+      <c r="AG11" s="130"/>
+      <c r="AH11" s="130"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="87"/>
       <c r="AK11" s="87"/>
@@ -2851,54 +2905,54 @@
       <c r="A12" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="138" t="s">
+      <c r="B12" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="138"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="137"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="138"/>
       <c r="M12" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="136"/>
-      <c r="O12" s="137"/>
+      <c r="N12" s="137"/>
+      <c r="O12" s="138"/>
       <c r="P12" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="134"/>
-      <c r="R12" s="130"/>
-      <c r="S12" s="130"/>
-      <c r="T12" s="131"/>
-      <c r="U12" s="132" t="s">
+      <c r="Q12" s="135"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="V12" s="133"/>
+      <c r="V12" s="134"/>
       <c r="W12" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="X12" s="140" t="s">
+      <c r="X12" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="Y12" s="140"/>
-      <c r="Z12" s="140"/>
-      <c r="AA12" s="106"/>
-      <c r="AB12" s="108"/>
+      <c r="Y12" s="141"/>
+      <c r="Z12" s="141"/>
+      <c r="AA12" s="107"/>
+      <c r="AB12" s="109"/>
       <c r="AC12" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="AD12" s="134"/>
-      <c r="AE12" s="130"/>
-      <c r="AF12" s="130"/>
-      <c r="AG12" s="131"/>
-      <c r="AH12" s="134"/>
-      <c r="AI12" s="133"/>
+      <c r="AD12" s="135"/>
+      <c r="AE12" s="131"/>
+      <c r="AF12" s="131"/>
+      <c r="AG12" s="132"/>
+      <c r="AH12" s="135"/>
+      <c r="AI12" s="134"/>
       <c r="AJ12" s="87"/>
       <c r="AK12" s="87"/>
       <c r="AL12" s="87"/>
@@ -2922,46 +2976,46 @@
     </row>
     <row r="13" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="J13" s="115" t="s">
+      <c r="J13" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="115"/>
-      <c r="L13" s="115"/>
-      <c r="M13" s="115"/>
-      <c r="N13" s="115"/>
-      <c r="O13" s="115"/>
-      <c r="Q13" s="126" t="s">
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="116"/>
+      <c r="N13" s="116"/>
+      <c r="O13" s="116"/>
+      <c r="Q13" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="126"/>
-      <c r="S13" s="126" t="s">
+      <c r="R13" s="127"/>
+      <c r="S13" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="T13" s="126"/>
-      <c r="U13" s="126" t="s">
+      <c r="T13" s="127"/>
+      <c r="U13" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="V13" s="126"/>
+      <c r="V13" s="127"/>
       <c r="W13" s="5"/>
-      <c r="X13" s="110" t="s">
+      <c r="X13" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="Y13" s="110"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="110"/>
-      <c r="AB13" s="110"/>
-      <c r="AD13" s="126" t="s">
+      <c r="Y13" s="111"/>
+      <c r="Z13" s="111"/>
+      <c r="AA13" s="111"/>
+      <c r="AB13" s="111"/>
+      <c r="AD13" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="AE13" s="126"/>
-      <c r="AF13" s="126" t="s">
+      <c r="AE13" s="127"/>
+      <c r="AF13" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="AG13" s="126"/>
-      <c r="AH13" s="126" t="s">
+      <c r="AG13" s="127"/>
+      <c r="AH13" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="AI13" s="126"/>
+      <c r="AI13" s="127"/>
       <c r="AJ13" s="87"/>
       <c r="AK13" s="87"/>
       <c r="AL13" s="87"/>
@@ -2985,51 +3039,51 @@
     </row>
     <row r="14" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31"/>
-      <c r="B14" s="127" t="s">
+      <c r="B14" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="107"/>
-      <c r="I14" s="107"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="127" t="s">
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="128" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="128"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="127" t="s">
+      <c r="L14" s="128"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="107"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="T14" s="127"/>
-      <c r="U14" s="127"/>
-      <c r="V14" s="127"/>
-      <c r="W14" s="127"/>
-      <c r="X14" s="128"/>
-      <c r="Y14" s="136"/>
-      <c r="Z14" s="137"/>
-      <c r="AA14" s="135" t="s">
+      <c r="T14" s="128"/>
+      <c r="U14" s="128"/>
+      <c r="V14" s="128"/>
+      <c r="W14" s="128"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="137"/>
+      <c r="Z14" s="138"/>
+      <c r="AA14" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="AB14" s="135"/>
-      <c r="AC14" s="147" t="s">
+      <c r="AB14" s="136"/>
+      <c r="AC14" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="AD14" s="147"/>
-      <c r="AE14" s="147"/>
-      <c r="AF14" s="147"/>
-      <c r="AG14" s="145">
+      <c r="AD14" s="148"/>
+      <c r="AE14" s="148"/>
+      <c r="AF14" s="148"/>
+      <c r="AG14" s="146">
         <v>1</v>
       </c>
-      <c r="AH14" s="146"/>
+      <c r="AH14" s="147"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="87"/>
       <c r="AK14" s="87"/>
@@ -3055,46 +3109,46 @@
     <row r="15" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116" t="s">
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
-      <c r="S15" s="116" t="s">
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="T15" s="116"/>
-      <c r="U15" s="116"/>
-      <c r="V15" s="116"/>
-      <c r="W15" s="116"/>
-      <c r="X15" s="116"/>
-      <c r="Y15" s="116"/>
-      <c r="Z15" s="116"/>
-      <c r="AA15" s="116" t="s">
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="AB15" s="116"/>
-      <c r="AC15" s="116"/>
-      <c r="AD15" s="116"/>
-      <c r="AE15" s="116"/>
-      <c r="AF15" s="116"/>
-      <c r="AG15" s="116"/>
-      <c r="AH15" s="116"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="117"/>
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="117"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="117"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="87"/>
       <c r="AK15" s="87"/>
@@ -3120,38 +3174,38 @@
     <row r="16" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
       <c r="B16" s="24"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="112"/>
-      <c r="U16" s="112"/>
-      <c r="V16" s="112"/>
-      <c r="W16" s="112"/>
-      <c r="X16" s="112"/>
-      <c r="Y16" s="112"/>
-      <c r="Z16" s="113"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="112"/>
-      <c r="AD16" s="112"/>
-      <c r="AE16" s="112"/>
-      <c r="AF16" s="112"/>
-      <c r="AG16" s="112"/>
-      <c r="AH16" s="113"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="112"/>
+      <c r="T16" s="113"/>
+      <c r="U16" s="113"/>
+      <c r="V16" s="113"/>
+      <c r="W16" s="113"/>
+      <c r="X16" s="113"/>
+      <c r="Y16" s="113"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="112"/>
+      <c r="AB16" s="113"/>
+      <c r="AC16" s="113"/>
+      <c r="AD16" s="113"/>
+      <c r="AE16" s="113"/>
+      <c r="AF16" s="113"/>
+      <c r="AG16" s="113"/>
+      <c r="AH16" s="114"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="87"/>
       <c r="AK16" s="93" t="s">
@@ -3174,54 +3228,54 @@
     </row>
     <row r="17" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32"/>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="119"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="119" t="s">
+      <c r="D17" s="120"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="119"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="113"/>
-      <c r="K17" s="119" t="s">
+      <c r="H17" s="120"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="L17" s="119"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="119" t="s">
+      <c r="L17" s="120"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="145"/>
+      <c r="O17" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="P17" s="119"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="113"/>
-      <c r="S17" s="119" t="s">
+      <c r="P17" s="120"/>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="T17" s="119"/>
-      <c r="U17" s="111"/>
-      <c r="V17" s="113"/>
-      <c r="W17" s="119" t="s">
+      <c r="T17" s="120"/>
+      <c r="U17" s="112"/>
+      <c r="V17" s="114"/>
+      <c r="W17" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="X17" s="119"/>
-      <c r="Y17" s="111"/>
-      <c r="Z17" s="113"/>
-      <c r="AA17" s="119" t="s">
+      <c r="X17" s="120"/>
+      <c r="Y17" s="112"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="AB17" s="119"/>
-      <c r="AC17" s="111"/>
-      <c r="AD17" s="113"/>
-      <c r="AE17" s="119" t="s">
+      <c r="AB17" s="120"/>
+      <c r="AC17" s="112"/>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="AF17" s="119"/>
-      <c r="AG17" s="111"/>
-      <c r="AH17" s="113"/>
+      <c r="AF17" s="120"/>
+      <c r="AG17" s="112"/>
+      <c r="AH17" s="114"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="87"/>
       <c r="AK17" s="94" t="s">
@@ -3244,41 +3298,41 @@
     </row>
     <row r="18" spans="1:45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32"/>
-      <c r="B18" s="142" t="s">
+      <c r="B18" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="142"/>
-      <c r="H18" s="142"/>
-      <c r="I18" s="142"/>
-      <c r="J18" s="142"/>
-      <c r="K18" s="142"/>
-      <c r="L18" s="142"/>
-      <c r="M18" s="142"/>
-      <c r="N18" s="142"/>
-      <c r="O18" s="142"/>
-      <c r="P18" s="142"/>
-      <c r="Q18" s="142"/>
-      <c r="R18" s="142"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="142"/>
-      <c r="U18" s="142"/>
-      <c r="V18" s="142"/>
-      <c r="W18" s="142"/>
-      <c r="X18" s="142"/>
-      <c r="Y18" s="142"/>
-      <c r="Z18" s="142"/>
-      <c r="AA18" s="142"/>
-      <c r="AB18" s="142"/>
-      <c r="AC18" s="142"/>
-      <c r="AD18" s="142"/>
-      <c r="AE18" s="142"/>
-      <c r="AF18" s="142"/>
-      <c r="AG18" s="142"/>
-      <c r="AH18" s="142"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="143"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="143"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="143"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="143"/>
+      <c r="V18" s="143"/>
+      <c r="W18" s="143"/>
+      <c r="X18" s="143"/>
+      <c r="Y18" s="143"/>
+      <c r="Z18" s="143"/>
+      <c r="AA18" s="143"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="143"/>
+      <c r="AD18" s="143"/>
+      <c r="AE18" s="143"/>
+      <c r="AF18" s="143"/>
+      <c r="AG18" s="143"/>
+      <c r="AH18" s="143"/>
       <c r="AJ18" s="87"/>
       <c r="AK18" s="94" t="s">
         <v>80</v>
@@ -3298,39 +3352,39 @@
     </row>
     <row r="19" spans="1:45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="123"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="124"/>
-      <c r="U19" s="125"/>
-      <c r="W19" s="111"/>
-      <c r="X19" s="113"/>
-      <c r="Z19" s="111"/>
-      <c r="AA19" s="113"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="125"/>
+      <c r="P19" s="125"/>
+      <c r="Q19" s="125"/>
+      <c r="R19" s="125"/>
+      <c r="S19" s="125"/>
+      <c r="T19" s="125"/>
+      <c r="U19" s="126"/>
+      <c r="W19" s="112"/>
+      <c r="X19" s="114"/>
+      <c r="Z19" s="112"/>
+      <c r="AA19" s="114"/>
       <c r="AB19" s="34"/>
-      <c r="AC19" s="111"/>
-      <c r="AD19" s="113"/>
+      <c r="AC19" s="112"/>
+      <c r="AD19" s="114"/>
       <c r="AE19" s="34"/>
-      <c r="AF19" s="111"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="113"/>
+      <c r="AF19" s="112"/>
+      <c r="AG19" s="113"/>
+      <c r="AH19" s="114"/>
       <c r="AJ19" s="87"/>
       <c r="AK19" s="94" t="s">
         <v>81</v>
@@ -3349,50 +3403,50 @@
       <c r="AS19" s="87"/>
     </row>
     <row r="20" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="114" t="s">
+      <c r="A20" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="152"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="152"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="152"/>
-      <c r="M20" s="152"/>
-      <c r="N20" s="152"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="152"/>
-      <c r="Q20" s="152"/>
-      <c r="R20" s="152"/>
-      <c r="S20" s="152"/>
-      <c r="T20" s="152"/>
-      <c r="U20" s="152"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="153"/>
+      <c r="N20" s="153"/>
+      <c r="O20" s="153"/>
+      <c r="P20" s="153"/>
+      <c r="Q20" s="153"/>
+      <c r="R20" s="153"/>
+      <c r="S20" s="153"/>
+      <c r="T20" s="153"/>
+      <c r="U20" s="153"/>
       <c r="V20" s="35"/>
-      <c r="W20" s="115" t="s">
+      <c r="W20" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="X20" s="115"/>
+      <c r="X20" s="116"/>
       <c r="Y20" s="36"/>
-      <c r="Z20" s="115" t="s">
+      <c r="Z20" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="AA20" s="115"/>
+      <c r="AA20" s="116"/>
       <c r="AB20" s="36"/>
-      <c r="AC20" s="115" t="s">
+      <c r="AC20" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="AD20" s="115"/>
+      <c r="AD20" s="116"/>
       <c r="AE20" s="36"/>
-      <c r="AF20" s="115" t="s">
+      <c r="AF20" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="AG20" s="115"/>
-      <c r="AH20" s="115"/>
+      <c r="AG20" s="116"/>
+      <c r="AH20" s="116"/>
       <c r="AJ20" s="87"/>
       <c r="AK20" s="94" t="s">
         <v>82</v>
@@ -3412,39 +3466,39 @@
     </row>
     <row r="21" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
-      <c r="B21" s="117" t="s">
+      <c r="B21" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
-      <c r="T21" s="124"/>
-      <c r="U21" s="125"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="113"/>
-      <c r="Z21" s="111"/>
-      <c r="AA21" s="113"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="125"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="125"/>
+      <c r="T21" s="125"/>
+      <c r="U21" s="126"/>
+      <c r="W21" s="112"/>
+      <c r="X21" s="114"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="114"/>
       <c r="AB21" s="34"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="113"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="114"/>
       <c r="AE21" s="34"/>
-      <c r="AF21" s="111"/>
-      <c r="AG21" s="112"/>
-      <c r="AH21" s="113"/>
+      <c r="AF21" s="112"/>
+      <c r="AG21" s="113"/>
+      <c r="AH21" s="114"/>
       <c r="AJ21" s="87"/>
       <c r="AK21" s="94" t="s">
         <v>83</v>
@@ -3463,50 +3517,50 @@
       <c r="AS21" s="87"/>
     </row>
     <row r="22" spans="1:45" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="109" t="s">
+      <c r="A22" s="110" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="109"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="109"/>
-      <c r="S22" s="109"/>
-      <c r="T22" s="109"/>
-      <c r="U22" s="109"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="110"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="110"/>
+      <c r="O22" s="110"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="110"/>
+      <c r="S22" s="110"/>
+      <c r="T22" s="110"/>
+      <c r="U22" s="110"/>
       <c r="V22" s="37"/>
-      <c r="W22" s="148" t="s">
+      <c r="W22" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="X22" s="148"/>
+      <c r="X22" s="149"/>
       <c r="Y22" s="38"/>
-      <c r="Z22" s="148" t="s">
+      <c r="Z22" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="AA22" s="148"/>
+      <c r="AA22" s="149"/>
       <c r="AB22" s="38"/>
-      <c r="AC22" s="148" t="s">
+      <c r="AC22" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="AD22" s="148"/>
+      <c r="AD22" s="149"/>
       <c r="AE22" s="38"/>
-      <c r="AF22" s="148" t="s">
+      <c r="AF22" s="149" t="s">
         <v>50</v>
       </c>
-      <c r="AG22" s="148"/>
-      <c r="AH22" s="148"/>
+      <c r="AG22" s="149"/>
+      <c r="AH22" s="149"/>
       <c r="AI22" s="39"/>
       <c r="AJ22" s="87"/>
       <c r="AK22" s="94" t="s">
@@ -3582,54 +3636,54 @@
       <c r="A24" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="138"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="137"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="137"/>
+      <c r="K24" s="142"/>
+      <c r="L24" s="138"/>
       <c r="M24" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="136"/>
-      <c r="O24" s="137"/>
+      <c r="N24" s="137"/>
+      <c r="O24" s="138"/>
       <c r="P24" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="130"/>
-      <c r="S24" s="130"/>
-      <c r="T24" s="131"/>
-      <c r="U24" s="132" t="s">
+      <c r="Q24" s="135"/>
+      <c r="R24" s="131"/>
+      <c r="S24" s="131"/>
+      <c r="T24" s="132"/>
+      <c r="U24" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="V24" s="133"/>
+      <c r="V24" s="134"/>
       <c r="W24" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="X24" s="140" t="s">
+      <c r="X24" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="Y24" s="140"/>
-      <c r="Z24" s="140"/>
-      <c r="AA24" s="106"/>
-      <c r="AB24" s="108"/>
+      <c r="Y24" s="141"/>
+      <c r="Z24" s="141"/>
+      <c r="AA24" s="107"/>
+      <c r="AB24" s="109"/>
       <c r="AC24" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="AD24" s="134"/>
-      <c r="AE24" s="130"/>
-      <c r="AF24" s="130"/>
-      <c r="AG24" s="131"/>
-      <c r="AH24" s="134"/>
-      <c r="AI24" s="133"/>
+      <c r="AD24" s="135"/>
+      <c r="AE24" s="131"/>
+      <c r="AF24" s="131"/>
+      <c r="AG24" s="132"/>
+      <c r="AH24" s="135"/>
+      <c r="AI24" s="134"/>
       <c r="AJ24" s="87"/>
       <c r="AK24" s="94" t="s">
         <v>86</v>
@@ -3649,46 +3703,46 @@
     </row>
     <row r="25" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26"/>
-      <c r="J25" s="196" t="s">
+      <c r="J25" s="197" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="196"/>
-      <c r="L25" s="196"/>
-      <c r="M25" s="196"/>
-      <c r="N25" s="196"/>
-      <c r="O25" s="196"/>
-      <c r="Q25" s="126" t="s">
+      <c r="K25" s="197"/>
+      <c r="L25" s="197"/>
+      <c r="M25" s="197"/>
+      <c r="N25" s="197"/>
+      <c r="O25" s="197"/>
+      <c r="Q25" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="R25" s="126"/>
-      <c r="S25" s="126" t="s">
+      <c r="R25" s="127"/>
+      <c r="S25" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="T25" s="126"/>
-      <c r="U25" s="126" t="s">
+      <c r="T25" s="127"/>
+      <c r="U25" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="V25" s="126"/>
+      <c r="V25" s="127"/>
       <c r="W25" s="5"/>
-      <c r="X25" s="110" t="s">
+      <c r="X25" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="Y25" s="110"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="110"/>
-      <c r="AB25" s="110"/>
-      <c r="AD25" s="126" t="s">
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="111"/>
+      <c r="AA25" s="111"/>
+      <c r="AB25" s="111"/>
+      <c r="AD25" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="AE25" s="126"/>
-      <c r="AF25" s="126" t="s">
+      <c r="AE25" s="127"/>
+      <c r="AF25" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="AG25" s="126"/>
-      <c r="AH25" s="126" t="s">
+      <c r="AG25" s="127"/>
+      <c r="AH25" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="AI25" s="126"/>
+      <c r="AI25" s="127"/>
       <c r="AJ25" s="87"/>
       <c r="AK25" s="94" t="s">
         <v>87</v>
@@ -3708,51 +3762,51 @@
     </row>
     <row r="26" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31"/>
-      <c r="B26" s="127" t="s">
+      <c r="B26" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="107"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="149" t="s">
+      <c r="C26" s="128"/>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="150" t="s">
         <v>44</v>
       </c>
-      <c r="L26" s="117"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="150"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="107"/>
-      <c r="R26" s="108"/>
-      <c r="S26" s="127" t="s">
+      <c r="L26" s="118"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="151"/>
+      <c r="O26" s="107"/>
+      <c r="P26" s="108"/>
+      <c r="Q26" s="108"/>
+      <c r="R26" s="109"/>
+      <c r="S26" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="T26" s="127"/>
-      <c r="U26" s="127"/>
-      <c r="V26" s="127"/>
-      <c r="W26" s="127"/>
-      <c r="X26" s="128"/>
-      <c r="Y26" s="136"/>
-      <c r="Z26" s="137"/>
-      <c r="AA26" s="135" t="s">
+      <c r="T26" s="128"/>
+      <c r="U26" s="128"/>
+      <c r="V26" s="128"/>
+      <c r="W26" s="128"/>
+      <c r="X26" s="129"/>
+      <c r="Y26" s="137"/>
+      <c r="Z26" s="138"/>
+      <c r="AA26" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="AB26" s="135"/>
-      <c r="AC26" s="147" t="s">
+      <c r="AB26" s="136"/>
+      <c r="AC26" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="AD26" s="147"/>
-      <c r="AE26" s="147"/>
-      <c r="AF26" s="147"/>
-      <c r="AG26" s="145">
+      <c r="AD26" s="148"/>
+      <c r="AE26" s="148"/>
+      <c r="AF26" s="148"/>
+      <c r="AG26" s="146">
         <v>1</v>
       </c>
-      <c r="AH26" s="146"/>
+      <c r="AH26" s="147"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="87"/>
       <c r="AK26" s="87"/>
@@ -3772,46 +3826,46 @@
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="116" t="s">
+      <c r="C27" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116" t="s">
+      <c r="D27" s="117"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="L27" s="116"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="116"/>
-      <c r="O27" s="116"/>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="116"/>
-      <c r="S27" s="116" t="s">
+      <c r="L27" s="117"/>
+      <c r="M27" s="117"/>
+      <c r="N27" s="117"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="117"/>
+      <c r="S27" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="T27" s="116"/>
-      <c r="U27" s="116"/>
-      <c r="V27" s="116"/>
-      <c r="W27" s="116"/>
-      <c r="X27" s="116"/>
-      <c r="Y27" s="116"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="116" t="s">
+      <c r="T27" s="117"/>
+      <c r="U27" s="117"/>
+      <c r="V27" s="117"/>
+      <c r="W27" s="117"/>
+      <c r="X27" s="117"/>
+      <c r="Y27" s="117"/>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="AB27" s="116"/>
-      <c r="AC27" s="116"/>
-      <c r="AD27" s="116"/>
-      <c r="AE27" s="116"/>
-      <c r="AF27" s="116"/>
-      <c r="AG27" s="116"/>
-      <c r="AH27" s="116"/>
+      <c r="AB27" s="117"/>
+      <c r="AC27" s="117"/>
+      <c r="AD27" s="117"/>
+      <c r="AE27" s="117"/>
+      <c r="AF27" s="117"/>
+      <c r="AG27" s="117"/>
+      <c r="AH27" s="117"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="87"/>
       <c r="AK27" s="87"/>
@@ -3831,38 +3885,38 @@
     <row r="28" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="111"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="112"/>
-      <c r="J28" s="113"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="112"/>
-      <c r="R28" s="113"/>
-      <c r="S28" s="111"/>
-      <c r="T28" s="112"/>
-      <c r="U28" s="112"/>
-      <c r="V28" s="112"/>
-      <c r="W28" s="112"/>
-      <c r="X28" s="112"/>
-      <c r="Y28" s="112"/>
-      <c r="Z28" s="113"/>
-      <c r="AA28" s="111"/>
-      <c r="AB28" s="112"/>
-      <c r="AC28" s="112"/>
-      <c r="AD28" s="112"/>
-      <c r="AE28" s="112"/>
-      <c r="AF28" s="112"/>
-      <c r="AG28" s="112"/>
-      <c r="AH28" s="113"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="112"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="113"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="113"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="112"/>
+      <c r="T28" s="113"/>
+      <c r="U28" s="113"/>
+      <c r="V28" s="113"/>
+      <c r="W28" s="113"/>
+      <c r="X28" s="113"/>
+      <c r="Y28" s="113"/>
+      <c r="Z28" s="114"/>
+      <c r="AA28" s="112"/>
+      <c r="AB28" s="113"/>
+      <c r="AC28" s="113"/>
+      <c r="AD28" s="113"/>
+      <c r="AE28" s="113"/>
+      <c r="AF28" s="113"/>
+      <c r="AG28" s="113"/>
+      <c r="AH28" s="114"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="87"/>
       <c r="AK28" s="87"/>
@@ -3881,54 +3935,54 @@
     </row>
     <row r="29" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="32"/>
-      <c r="C29" s="119" t="s">
+      <c r="C29" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="119"/>
-      <c r="E29" s="111"/>
-      <c r="F29" s="113"/>
-      <c r="G29" s="119" t="s">
+      <c r="D29" s="120"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="114"/>
+      <c r="G29" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="H29" s="119"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="119" t="s">
+      <c r="H29" s="120"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="119"/>
-      <c r="M29" s="143"/>
-      <c r="N29" s="144"/>
-      <c r="O29" s="119" t="s">
+      <c r="L29" s="120"/>
+      <c r="M29" s="144"/>
+      <c r="N29" s="145"/>
+      <c r="O29" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="111"/>
-      <c r="R29" s="113"/>
-      <c r="S29" s="119" t="s">
+      <c r="P29" s="120"/>
+      <c r="Q29" s="112"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="T29" s="119"/>
-      <c r="U29" s="111"/>
-      <c r="V29" s="113"/>
-      <c r="W29" s="119" t="s">
+      <c r="T29" s="120"/>
+      <c r="U29" s="112"/>
+      <c r="V29" s="114"/>
+      <c r="W29" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="X29" s="119"/>
-      <c r="Y29" s="111"/>
-      <c r="Z29" s="113"/>
-      <c r="AA29" s="119" t="s">
+      <c r="X29" s="120"/>
+      <c r="Y29" s="112"/>
+      <c r="Z29" s="114"/>
+      <c r="AA29" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="AB29" s="119"/>
-      <c r="AC29" s="111"/>
-      <c r="AD29" s="113"/>
-      <c r="AE29" s="119" t="s">
+      <c r="AB29" s="120"/>
+      <c r="AC29" s="112"/>
+      <c r="AD29" s="114"/>
+      <c r="AE29" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="AF29" s="119"/>
-      <c r="AG29" s="111"/>
-      <c r="AH29" s="113"/>
+      <c r="AF29" s="120"/>
+      <c r="AG29" s="112"/>
+      <c r="AH29" s="114"/>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="87"/>
       <c r="AK29" s="87"/>
@@ -3947,41 +4001,41 @@
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="32"/>
-      <c r="B30" s="142" t="s">
+      <c r="B30" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="142"/>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="142"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="142"/>
-      <c r="M30" s="142"/>
-      <c r="N30" s="142"/>
-      <c r="O30" s="142"/>
-      <c r="P30" s="142"/>
-      <c r="Q30" s="142"/>
-      <c r="R30" s="142"/>
-      <c r="S30" s="142"/>
-      <c r="T30" s="142"/>
-      <c r="U30" s="142"/>
-      <c r="V30" s="142"/>
-      <c r="W30" s="142"/>
-      <c r="X30" s="142"/>
-      <c r="Y30" s="142"/>
-      <c r="Z30" s="142"/>
-      <c r="AA30" s="142"/>
-      <c r="AB30" s="142"/>
-      <c r="AC30" s="142"/>
-      <c r="AD30" s="142"/>
-      <c r="AE30" s="142"/>
-      <c r="AF30" s="142"/>
-      <c r="AG30" s="142"/>
-      <c r="AH30" s="142"/>
+      <c r="C30" s="143"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="143"/>
+      <c r="Q30" s="143"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="143"/>
+      <c r="T30" s="143"/>
+      <c r="U30" s="143"/>
+      <c r="V30" s="143"/>
+      <c r="W30" s="143"/>
+      <c r="X30" s="143"/>
+      <c r="Y30" s="143"/>
+      <c r="Z30" s="143"/>
+      <c r="AA30" s="143"/>
+      <c r="AB30" s="143"/>
+      <c r="AC30" s="143"/>
+      <c r="AD30" s="143"/>
+      <c r="AE30" s="143"/>
+      <c r="AF30" s="143"/>
+      <c r="AG30" s="143"/>
+      <c r="AH30" s="143"/>
       <c r="AJ30" s="87"/>
       <c r="AK30" s="87"/>
       <c r="AL30" s="87"/>
@@ -3999,39 +4053,39 @@
     </row>
     <row r="31" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32"/>
-      <c r="B31" s="117" t="s">
+      <c r="B31" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="123"/>
-      <c r="N31" s="124"/>
-      <c r="O31" s="124"/>
-      <c r="P31" s="124"/>
-      <c r="Q31" s="124"/>
-      <c r="R31" s="124"/>
-      <c r="S31" s="124"/>
-      <c r="T31" s="124"/>
-      <c r="U31" s="125"/>
-      <c r="W31" s="111"/>
-      <c r="X31" s="113"/>
-      <c r="Z31" s="111"/>
-      <c r="AA31" s="113"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="124"/>
+      <c r="N31" s="125"/>
+      <c r="O31" s="125"/>
+      <c r="P31" s="125"/>
+      <c r="Q31" s="125"/>
+      <c r="R31" s="125"/>
+      <c r="S31" s="125"/>
+      <c r="T31" s="125"/>
+      <c r="U31" s="126"/>
+      <c r="W31" s="112"/>
+      <c r="X31" s="114"/>
+      <c r="Z31" s="112"/>
+      <c r="AA31" s="114"/>
       <c r="AB31" s="34"/>
-      <c r="AC31" s="111"/>
-      <c r="AD31" s="113"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="114"/>
       <c r="AE31" s="34"/>
-      <c r="AF31" s="111"/>
-      <c r="AG31" s="112"/>
-      <c r="AH31" s="113"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="113"/>
+      <c r="AH31" s="114"/>
       <c r="AJ31" s="87"/>
       <c r="AK31" s="87"/>
       <c r="AL31" s="87"/>
@@ -4048,50 +4102,50 @@
       <c r="AS31" s="87"/>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="114" t="s">
+      <c r="A32" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="152"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152"/>
-      <c r="G32" s="152"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="152"/>
-      <c r="J32" s="152"/>
-      <c r="K32" s="152"/>
-      <c r="L32" s="152"/>
-      <c r="M32" s="152"/>
-      <c r="N32" s="152"/>
-      <c r="O32" s="152"/>
-      <c r="P32" s="152"/>
-      <c r="Q32" s="152"/>
-      <c r="R32" s="152"/>
-      <c r="S32" s="152"/>
-      <c r="T32" s="152"/>
-      <c r="U32" s="152"/>
+      <c r="B32" s="153"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="153"/>
+      <c r="N32" s="153"/>
+      <c r="O32" s="153"/>
+      <c r="P32" s="153"/>
+      <c r="Q32" s="153"/>
+      <c r="R32" s="153"/>
+      <c r="S32" s="153"/>
+      <c r="T32" s="153"/>
+      <c r="U32" s="153"/>
       <c r="V32" s="35"/>
-      <c r="W32" s="115" t="s">
+      <c r="W32" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="X32" s="115"/>
+      <c r="X32" s="116"/>
       <c r="Y32" s="36"/>
-      <c r="Z32" s="115" t="s">
+      <c r="Z32" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="AA32" s="115"/>
+      <c r="AA32" s="116"/>
       <c r="AB32" s="36"/>
-      <c r="AC32" s="115" t="s">
+      <c r="AC32" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="AD32" s="115"/>
+      <c r="AD32" s="116"/>
       <c r="AE32" s="36"/>
-      <c r="AF32" s="115" t="s">
+      <c r="AF32" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="AG32" s="115"/>
-      <c r="AH32" s="115"/>
+      <c r="AG32" s="116"/>
+      <c r="AH32" s="116"/>
       <c r="AJ32" s="87"/>
       <c r="AK32" s="87"/>
       <c r="AL32" s="87"/>
@@ -4109,39 +4163,39 @@
     </row>
     <row r="33" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
-      <c r="B33" s="117" t="s">
+      <c r="B33" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="118"/>
-      <c r="M33" s="123"/>
-      <c r="N33" s="124"/>
-      <c r="O33" s="124"/>
-      <c r="P33" s="124"/>
-      <c r="Q33" s="124"/>
-      <c r="R33" s="124"/>
-      <c r="S33" s="124"/>
-      <c r="T33" s="124"/>
-      <c r="U33" s="125"/>
-      <c r="W33" s="111"/>
-      <c r="X33" s="113"/>
-      <c r="Z33" s="111"/>
-      <c r="AA33" s="113"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="118"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="119"/>
+      <c r="M33" s="124"/>
+      <c r="N33" s="125"/>
+      <c r="O33" s="125"/>
+      <c r="P33" s="125"/>
+      <c r="Q33" s="125"/>
+      <c r="R33" s="125"/>
+      <c r="S33" s="125"/>
+      <c r="T33" s="125"/>
+      <c r="U33" s="126"/>
+      <c r="W33" s="112"/>
+      <c r="X33" s="114"/>
+      <c r="Z33" s="112"/>
+      <c r="AA33" s="114"/>
       <c r="AB33" s="34"/>
-      <c r="AC33" s="111"/>
-      <c r="AD33" s="113"/>
+      <c r="AC33" s="112"/>
+      <c r="AD33" s="114"/>
       <c r="AE33" s="34"/>
-      <c r="AF33" s="111"/>
-      <c r="AG33" s="112"/>
-      <c r="AH33" s="113"/>
+      <c r="AF33" s="112"/>
+      <c r="AG33" s="113"/>
+      <c r="AH33" s="114"/>
       <c r="AJ33" s="87"/>
       <c r="AK33" s="87"/>
       <c r="AL33" s="87"/>
@@ -4158,50 +4212,50 @@
       <c r="AS33" s="87"/>
     </row>
     <row r="34" spans="1:50" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="114" t="s">
+      <c r="A34" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="114"/>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="114"/>
-      <c r="I34" s="114"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="114"/>
-      <c r="L34" s="114"/>
-      <c r="M34" s="114"/>
-      <c r="N34" s="114"/>
-      <c r="O34" s="114"/>
-      <c r="P34" s="114"/>
-      <c r="Q34" s="114"/>
-      <c r="R34" s="114"/>
-      <c r="S34" s="114"/>
-      <c r="T34" s="114"/>
-      <c r="U34" s="114"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="115"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="115"/>
+      <c r="J34" s="115"/>
+      <c r="K34" s="115"/>
+      <c r="L34" s="115"/>
+      <c r="M34" s="115"/>
+      <c r="N34" s="115"/>
+      <c r="O34" s="115"/>
+      <c r="P34" s="115"/>
+      <c r="Q34" s="115"/>
+      <c r="R34" s="115"/>
+      <c r="S34" s="115"/>
+      <c r="T34" s="115"/>
+      <c r="U34" s="115"/>
       <c r="V34" s="35"/>
-      <c r="W34" s="115" t="s">
+      <c r="W34" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="X34" s="115"/>
+      <c r="X34" s="116"/>
       <c r="Y34" s="36"/>
-      <c r="Z34" s="115" t="s">
+      <c r="Z34" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="AA34" s="115"/>
+      <c r="AA34" s="116"/>
       <c r="AB34" s="36"/>
-      <c r="AC34" s="115" t="s">
+      <c r="AC34" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="AD34" s="115"/>
+      <c r="AD34" s="116"/>
       <c r="AE34" s="36"/>
-      <c r="AF34" s="115" t="s">
+      <c r="AF34" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="AG34" s="115"/>
-      <c r="AH34" s="115"/>
+      <c r="AG34" s="116"/>
+      <c r="AH34" s="116"/>
       <c r="AJ34" s="87"/>
       <c r="AK34" s="87"/>
       <c r="AL34" s="87"/>
@@ -4218,43 +4272,43 @@
       <c r="AS34" s="87"/>
     </row>
     <row r="35" spans="1:50" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="151" t="s">
+      <c r="A35" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="151"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
-      <c r="I35" s="151"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="151"/>
-      <c r="L35" s="151"/>
-      <c r="M35" s="151"/>
-      <c r="N35" s="151"/>
-      <c r="O35" s="151"/>
-      <c r="P35" s="151"/>
-      <c r="Q35" s="151"/>
-      <c r="R35" s="151"/>
-      <c r="S35" s="151"/>
-      <c r="T35" s="151"/>
-      <c r="U35" s="151"/>
-      <c r="V35" s="151"/>
-      <c r="W35" s="151"/>
-      <c r="X35" s="151"/>
-      <c r="Y35" s="151"/>
-      <c r="Z35" s="151"/>
-      <c r="AA35" s="151"/>
-      <c r="AB35" s="151"/>
-      <c r="AC35" s="151"/>
-      <c r="AD35" s="151"/>
-      <c r="AE35" s="151"/>
-      <c r="AF35" s="151"/>
-      <c r="AG35" s="151"/>
-      <c r="AH35" s="151"/>
-      <c r="AI35" s="151"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+      <c r="I35" s="152"/>
+      <c r="J35" s="152"/>
+      <c r="K35" s="152"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="152"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
+      <c r="Q35" s="152"/>
+      <c r="R35" s="152"/>
+      <c r="S35" s="152"/>
+      <c r="T35" s="152"/>
+      <c r="U35" s="152"/>
+      <c r="V35" s="152"/>
+      <c r="W35" s="152"/>
+      <c r="X35" s="152"/>
+      <c r="Y35" s="152"/>
+      <c r="Z35" s="152"/>
+      <c r="AA35" s="152"/>
+      <c r="AB35" s="152"/>
+      <c r="AC35" s="152"/>
+      <c r="AD35" s="152"/>
+      <c r="AE35" s="152"/>
+      <c r="AF35" s="152"/>
+      <c r="AG35" s="152"/>
+      <c r="AH35" s="152"/>
+      <c r="AI35" s="152"/>
       <c r="AJ35" s="87"/>
       <c r="AK35" s="87"/>
       <c r="AL35" s="87"/>
@@ -4271,43 +4325,43 @@
       <c r="AS35" s="87"/>
     </row>
     <row r="36" spans="1:50" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="110" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="109"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="109"/>
-      <c r="E36" s="109"/>
-      <c r="F36" s="109"/>
-      <c r="G36" s="109"/>
-      <c r="H36" s="109"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="109"/>
-      <c r="K36" s="109"/>
-      <c r="L36" s="109"/>
-      <c r="M36" s="109"/>
-      <c r="N36" s="109"/>
-      <c r="O36" s="109"/>
-      <c r="P36" s="109"/>
-      <c r="Q36" s="109"/>
-      <c r="R36" s="109"/>
-      <c r="S36" s="109"/>
-      <c r="T36" s="109"/>
-      <c r="U36" s="109"/>
-      <c r="V36" s="109"/>
-      <c r="W36" s="109"/>
-      <c r="X36" s="109"/>
-      <c r="Y36" s="109"/>
-      <c r="Z36" s="109"/>
-      <c r="AA36" s="109"/>
-      <c r="AB36" s="109"/>
-      <c r="AC36" s="109"/>
-      <c r="AD36" s="109"/>
-      <c r="AE36" s="109"/>
-      <c r="AF36" s="109"/>
-      <c r="AG36" s="109"/>
-      <c r="AH36" s="109"/>
-      <c r="AI36" s="109"/>
+      <c r="B36" s="110"/>
+      <c r="C36" s="110"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="110"/>
+      <c r="G36" s="110"/>
+      <c r="H36" s="110"/>
+      <c r="I36" s="110"/>
+      <c r="J36" s="110"/>
+      <c r="K36" s="110"/>
+      <c r="L36" s="110"/>
+      <c r="M36" s="110"/>
+      <c r="N36" s="110"/>
+      <c r="O36" s="110"/>
+      <c r="P36" s="110"/>
+      <c r="Q36" s="110"/>
+      <c r="R36" s="110"/>
+      <c r="S36" s="110"/>
+      <c r="T36" s="110"/>
+      <c r="U36" s="110"/>
+      <c r="V36" s="110"/>
+      <c r="W36" s="110"/>
+      <c r="X36" s="110"/>
+      <c r="Y36" s="110"/>
+      <c r="Z36" s="110"/>
+      <c r="AA36" s="110"/>
+      <c r="AB36" s="110"/>
+      <c r="AC36" s="110"/>
+      <c r="AD36" s="110"/>
+      <c r="AE36" s="110"/>
+      <c r="AF36" s="110"/>
+      <c r="AG36" s="110"/>
+      <c r="AH36" s="110"/>
+      <c r="AI36" s="110"/>
       <c r="AJ36" s="87"/>
       <c r="AK36" s="87"/>
       <c r="AL36" s="87"/>
@@ -4362,7 +4416,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>31</v>
       </c>
@@ -4376,23 +4430,23 @@
       <c r="G38" s="198"/>
       <c r="H38" s="198"/>
       <c r="I38" s="198"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="112"/>
-      <c r="L38" s="112"/>
-      <c r="M38" s="112"/>
-      <c r="N38" s="112"/>
-      <c r="O38" s="112"/>
-      <c r="P38" s="112"/>
-      <c r="Q38" s="112"/>
-      <c r="R38" s="112"/>
-      <c r="S38" s="112"/>
-      <c r="T38" s="112"/>
-      <c r="U38" s="112"/>
-      <c r="V38" s="113"/>
-      <c r="W38" s="197" t="s">
+      <c r="J38" s="112"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="113"/>
+      <c r="O38" s="113"/>
+      <c r="P38" s="113"/>
+      <c r="Q38" s="113"/>
+      <c r="R38" s="113"/>
+      <c r="S38" s="113"/>
+      <c r="T38" s="113"/>
+      <c r="U38" s="113"/>
+      <c r="V38" s="114"/>
+      <c r="W38" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="X38" s="197"/>
+      <c r="X38" s="99"/>
       <c r="Y38" s="67"/>
       <c r="Z38" s="67"/>
       <c r="AA38" s="74"/>
@@ -4405,7 +4459,7 @@
       <c r="AH38" s="74"/>
       <c r="AI38" s="42"/>
     </row>
-    <row r="39" spans="1:50" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43"/>
       <c r="B39" s="44"/>
       <c r="C39" s="44"/>
@@ -4415,65 +4469,67 @@
       <c r="G39" s="45"/>
       <c r="H39" s="45"/>
       <c r="I39" s="45"/>
-      <c r="J39" s="153" t="s">
+      <c r="J39" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="K39" s="153"/>
-      <c r="L39" s="153"/>
-      <c r="M39" s="153"/>
-      <c r="N39" s="153"/>
-      <c r="O39" s="153"/>
-      <c r="P39" s="153"/>
-      <c r="Q39" s="153"/>
-      <c r="R39" s="153"/>
-      <c r="S39" s="153"/>
-      <c r="T39" s="153"/>
-      <c r="U39" s="153"/>
-      <c r="V39" s="153"/>
-      <c r="W39" s="45"/>
-      <c r="X39" s="45"/>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="45"/>
-      <c r="AD39" s="45"/>
-      <c r="AE39" s="45"/>
-      <c r="AF39" s="45"/>
-      <c r="AG39" s="45"/>
-      <c r="AH39" s="45"/>
+      <c r="K39" s="154"/>
+      <c r="L39" s="154"/>
+      <c r="M39" s="154"/>
+      <c r="N39" s="154"/>
+      <c r="O39" s="154"/>
+      <c r="P39" s="154"/>
+      <c r="Q39" s="154"/>
+      <c r="R39" s="154"/>
+      <c r="S39" s="154"/>
+      <c r="T39" s="154"/>
+      <c r="U39" s="154"/>
+      <c r="V39" s="154"/>
+      <c r="W39" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="X39" s="99"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="67"/>
+      <c r="AA39" s="74"/>
+      <c r="AB39" s="74"/>
+      <c r="AC39" s="74"/>
+      <c r="AD39" s="74"/>
+      <c r="AE39" s="74"/>
+      <c r="AF39" s="74"/>
+      <c r="AG39" s="75"/>
+      <c r="AH39" s="74"/>
       <c r="AI39" s="45"/>
     </row>
-    <row r="40" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26"/>
-      <c r="B40" s="117" t="s">
+      <c r="B40" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="117"/>
-      <c r="D40" s="117"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="117"/>
-      <c r="G40" s="117"/>
-      <c r="H40" s="117"/>
-      <c r="I40" s="117"/>
-      <c r="J40" s="117"/>
-      <c r="K40" s="117"/>
-      <c r="L40" s="117"/>
-      <c r="M40" s="117"/>
-      <c r="N40" s="117"/>
-      <c r="O40" s="117"/>
-      <c r="P40" s="117"/>
-      <c r="Q40" s="117"/>
-      <c r="R40" s="117"/>
-      <c r="S40" s="117"/>
-      <c r="T40" s="117"/>
-      <c r="U40" s="117"/>
-      <c r="V40" s="117"/>
-      <c r="W40" s="117"/>
-      <c r="X40" s="117"/>
-      <c r="Y40" s="117"/>
-      <c r="Z40" s="117"/>
-      <c r="AA40" s="117"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="118"/>
+      <c r="H40" s="118"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="118"/>
+      <c r="L40" s="118"/>
+      <c r="M40" s="118"/>
+      <c r="N40" s="118"/>
+      <c r="O40" s="118"/>
+      <c r="P40" s="118"/>
+      <c r="Q40" s="118"/>
+      <c r="R40" s="118"/>
+      <c r="S40" s="118"/>
+      <c r="T40" s="118"/>
+      <c r="U40" s="118"/>
+      <c r="V40" s="118"/>
+      <c r="W40" s="118"/>
+      <c r="X40" s="118"/>
+      <c r="Y40" s="118"/>
+      <c r="Z40" s="118"/>
+      <c r="AA40" s="118"/>
       <c r="AB40" s="46"/>
       <c r="AC40" s="46"/>
       <c r="AD40" s="46"/>
@@ -4518,56 +4574,56 @@
       <c r="T41" s="52"/>
       <c r="U41" s="28"/>
       <c r="V41" s="52"/>
-      <c r="W41" s="111"/>
-      <c r="X41" s="112"/>
-      <c r="Y41" s="112"/>
-      <c r="Z41" s="112"/>
-      <c r="AA41" s="112"/>
-      <c r="AB41" s="112"/>
-      <c r="AC41" s="112"/>
-      <c r="AD41" s="112"/>
-      <c r="AE41" s="112"/>
-      <c r="AF41" s="112"/>
-      <c r="AG41" s="112"/>
-      <c r="AH41" s="113"/>
+      <c r="W41" s="112"/>
+      <c r="X41" s="113"/>
+      <c r="Y41" s="113"/>
+      <c r="Z41" s="113"/>
+      <c r="AA41" s="113"/>
+      <c r="AB41" s="113"/>
+      <c r="AC41" s="113"/>
+      <c r="AD41" s="113"/>
+      <c r="AE41" s="113"/>
+      <c r="AF41" s="113"/>
+      <c r="AG41" s="113"/>
+      <c r="AH41" s="114"/>
       <c r="AI41" s="53"/>
     </row>
     <row r="42" spans="1:50" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="48"/>
       <c r="F42" s="54"/>
-      <c r="G42" s="129" t="s">
+      <c r="G42" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="K42" s="129" t="s">
+      <c r="H42" s="130"/>
+      <c r="I42" s="130"/>
+      <c r="K42" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="L42" s="129"/>
-      <c r="M42" s="129"/>
-      <c r="N42" s="129"/>
-      <c r="O42" s="129"/>
-      <c r="P42" s="129"/>
-      <c r="Q42" s="129"/>
-      <c r="R42" s="129"/>
-      <c r="S42" s="129"/>
+      <c r="L42" s="130"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="130"/>
+      <c r="O42" s="130"/>
+      <c r="P42" s="130"/>
+      <c r="Q42" s="130"/>
+      <c r="R42" s="130"/>
+      <c r="S42" s="130"/>
       <c r="T42" s="46"/>
       <c r="U42" s="55"/>
       <c r="V42" s="46"/>
-      <c r="W42" s="180" t="s">
+      <c r="W42" s="181" t="s">
         <v>26</v>
       </c>
-      <c r="X42" s="180"/>
-      <c r="Y42" s="180"/>
-      <c r="Z42" s="180"/>
-      <c r="AA42" s="180"/>
-      <c r="AB42" s="180"/>
-      <c r="AC42" s="180"/>
-      <c r="AD42" s="180"/>
-      <c r="AE42" s="180"/>
-      <c r="AF42" s="180"/>
-      <c r="AG42" s="180"/>
-      <c r="AH42" s="180"/>
+      <c r="X42" s="181"/>
+      <c r="Y42" s="181"/>
+      <c r="Z42" s="181"/>
+      <c r="AA42" s="181"/>
+      <c r="AB42" s="181"/>
+      <c r="AC42" s="181"/>
+      <c r="AD42" s="181"/>
+      <c r="AE42" s="181"/>
+      <c r="AF42" s="181"/>
+      <c r="AG42" s="181"/>
+      <c r="AH42" s="181"/>
       <c r="AI42" s="53"/>
     </row>
     <row r="43" spans="1:50" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4681,25 +4737,25 @@
       <c r="J45" s="202"/>
       <c r="K45" s="202"/>
       <c r="L45" s="202"/>
-      <c r="M45" s="111"/>
-      <c r="N45" s="112"/>
-      <c r="O45" s="112"/>
-      <c r="P45" s="112"/>
-      <c r="Q45" s="112"/>
-      <c r="R45" s="112"/>
-      <c r="S45" s="112"/>
-      <c r="T45" s="112"/>
-      <c r="U45" s="113"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="113"/>
+      <c r="O45" s="113"/>
+      <c r="P45" s="113"/>
+      <c r="Q45" s="113"/>
+      <c r="R45" s="113"/>
+      <c r="S45" s="113"/>
+      <c r="T45" s="113"/>
+      <c r="U45" s="114"/>
       <c r="V45" s="203" t="s">
         <v>16</v>
       </c>
       <c r="W45" s="204"/>
-      <c r="X45" s="134"/>
-      <c r="Y45" s="130"/>
-      <c r="Z45" s="130"/>
-      <c r="AA45" s="131"/>
-      <c r="AB45" s="134"/>
-      <c r="AC45" s="133"/>
+      <c r="X45" s="135"/>
+      <c r="Y45" s="131"/>
+      <c r="Z45" s="131"/>
+      <c r="AA45" s="132"/>
+      <c r="AB45" s="135"/>
+      <c r="AC45" s="134"/>
       <c r="AD45" s="79"/>
       <c r="AE45" s="79"/>
       <c r="AF45" s="79"/>
@@ -4792,109 +4848,109 @@
       <c r="AI47" s="22"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="B48" s="154"/>
-      <c r="C48" s="155"/>
-      <c r="D48" s="155"/>
-      <c r="E48" s="155"/>
-      <c r="F48" s="155"/>
-      <c r="G48" s="155"/>
-      <c r="H48" s="155"/>
-      <c r="I48" s="155"/>
-      <c r="J48" s="155"/>
-      <c r="K48" s="155"/>
-      <c r="L48" s="155"/>
-      <c r="M48" s="155"/>
-      <c r="N48" s="155"/>
-      <c r="O48" s="156"/>
-      <c r="Q48" s="187"/>
-      <c r="R48" s="188"/>
-      <c r="S48" s="188"/>
-      <c r="T48" s="188"/>
-      <c r="U48" s="188"/>
-      <c r="V48" s="188"/>
-      <c r="W48" s="188"/>
-      <c r="X48" s="189"/>
-      <c r="Z48" s="154"/>
-      <c r="AA48" s="155"/>
-      <c r="AB48" s="155"/>
-      <c r="AC48" s="155"/>
-      <c r="AD48" s="155"/>
-      <c r="AE48" s="155"/>
-      <c r="AF48" s="155"/>
-      <c r="AG48" s="155"/>
-      <c r="AH48" s="156"/>
+      <c r="B48" s="155"/>
+      <c r="C48" s="156"/>
+      <c r="D48" s="156"/>
+      <c r="E48" s="156"/>
+      <c r="F48" s="156"/>
+      <c r="G48" s="156"/>
+      <c r="H48" s="156"/>
+      <c r="I48" s="156"/>
+      <c r="J48" s="156"/>
+      <c r="K48" s="156"/>
+      <c r="L48" s="156"/>
+      <c r="M48" s="156"/>
+      <c r="N48" s="156"/>
+      <c r="O48" s="157"/>
+      <c r="Q48" s="188"/>
+      <c r="R48" s="189"/>
+      <c r="S48" s="189"/>
+      <c r="T48" s="189"/>
+      <c r="U48" s="189"/>
+      <c r="V48" s="189"/>
+      <c r="W48" s="189"/>
+      <c r="X48" s="190"/>
+      <c r="Z48" s="155"/>
+      <c r="AA48" s="156"/>
+      <c r="AB48" s="156"/>
+      <c r="AC48" s="156"/>
+      <c r="AD48" s="156"/>
+      <c r="AE48" s="156"/>
+      <c r="AF48" s="156"/>
+      <c r="AG48" s="156"/>
+      <c r="AH48" s="157"/>
       <c r="AI48" s="56"/>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="B49" s="157"/>
-      <c r="C49" s="158"/>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="158"/>
-      <c r="L49" s="158"/>
-      <c r="M49" s="158"/>
-      <c r="N49" s="158"/>
-      <c r="O49" s="159"/>
-      <c r="Q49" s="190"/>
-      <c r="R49" s="191"/>
-      <c r="S49" s="191"/>
-      <c r="T49" s="191"/>
-      <c r="U49" s="191"/>
-      <c r="V49" s="191"/>
-      <c r="W49" s="191"/>
-      <c r="X49" s="192"/>
-      <c r="Z49" s="157"/>
-      <c r="AA49" s="158"/>
-      <c r="AB49" s="158"/>
-      <c r="AC49" s="158"/>
-      <c r="AD49" s="158"/>
-      <c r="AE49" s="158"/>
-      <c r="AF49" s="158"/>
-      <c r="AG49" s="158"/>
-      <c r="AH49" s="159"/>
+    <row r="49" spans="1:35" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="158"/>
+      <c r="C49" s="159"/>
+      <c r="D49" s="159"/>
+      <c r="E49" s="159"/>
+      <c r="F49" s="159"/>
+      <c r="G49" s="159"/>
+      <c r="H49" s="159"/>
+      <c r="I49" s="159"/>
+      <c r="J49" s="159"/>
+      <c r="K49" s="159"/>
+      <c r="L49" s="159"/>
+      <c r="M49" s="159"/>
+      <c r="N49" s="159"/>
+      <c r="O49" s="160"/>
+      <c r="Q49" s="191"/>
+      <c r="R49" s="192"/>
+      <c r="S49" s="192"/>
+      <c r="T49" s="192"/>
+      <c r="U49" s="192"/>
+      <c r="V49" s="192"/>
+      <c r="W49" s="192"/>
+      <c r="X49" s="193"/>
+      <c r="Z49" s="158"/>
+      <c r="AA49" s="159"/>
+      <c r="AB49" s="159"/>
+      <c r="AC49" s="159"/>
+      <c r="AD49" s="159"/>
+      <c r="AE49" s="159"/>
+      <c r="AF49" s="159"/>
+      <c r="AG49" s="159"/>
+      <c r="AH49" s="160"/>
       <c r="AI49" s="56"/>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="B50" s="153" t="s">
+      <c r="B50" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="153"/>
-      <c r="D50" s="153"/>
-      <c r="E50" s="153"/>
-      <c r="F50" s="153"/>
-      <c r="G50" s="153"/>
-      <c r="H50" s="153"/>
-      <c r="I50" s="153"/>
-      <c r="J50" s="153"/>
-      <c r="K50" s="153"/>
-      <c r="L50" s="153"/>
-      <c r="M50" s="153"/>
-      <c r="N50" s="153"/>
-      <c r="O50" s="153"/>
-      <c r="Q50" s="193"/>
-      <c r="R50" s="194"/>
-      <c r="S50" s="194"/>
-      <c r="T50" s="194"/>
-      <c r="U50" s="194"/>
-      <c r="V50" s="194"/>
-      <c r="W50" s="194"/>
-      <c r="X50" s="195"/>
-      <c r="Z50" s="129" t="s">
+      <c r="C50" s="154"/>
+      <c r="D50" s="154"/>
+      <c r="E50" s="154"/>
+      <c r="F50" s="154"/>
+      <c r="G50" s="154"/>
+      <c r="H50" s="154"/>
+      <c r="I50" s="154"/>
+      <c r="J50" s="154"/>
+      <c r="K50" s="154"/>
+      <c r="L50" s="154"/>
+      <c r="M50" s="154"/>
+      <c r="N50" s="154"/>
+      <c r="O50" s="154"/>
+      <c r="Q50" s="194"/>
+      <c r="R50" s="195"/>
+      <c r="S50" s="195"/>
+      <c r="T50" s="195"/>
+      <c r="U50" s="195"/>
+      <c r="V50" s="195"/>
+      <c r="W50" s="195"/>
+      <c r="X50" s="196"/>
+      <c r="Z50" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="AA50" s="129"/>
-      <c r="AB50" s="129"/>
-      <c r="AC50" s="129"/>
-      <c r="AD50" s="129"/>
-      <c r="AE50" s="129"/>
-      <c r="AF50" s="129"/>
-      <c r="AG50" s="129"/>
-      <c r="AH50" s="129"/>
+      <c r="AA50" s="130"/>
+      <c r="AB50" s="130"/>
+      <c r="AC50" s="130"/>
+      <c r="AD50" s="130"/>
+      <c r="AE50" s="130"/>
+      <c r="AF50" s="130"/>
+      <c r="AG50" s="130"/>
+      <c r="AH50" s="130"/>
       <c r="AI50" s="5"/>
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
@@ -4902,16 +4958,16 @@
         <v>8</v>
       </c>
       <c r="O51" s="57"/>
-      <c r="Q51" s="129" t="s">
+      <c r="Q51" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="R51" s="129"/>
-      <c r="S51" s="129"/>
-      <c r="T51" s="129"/>
-      <c r="U51" s="129"/>
-      <c r="V51" s="129"/>
-      <c r="W51" s="129"/>
-      <c r="X51" s="129"/>
+      <c r="R51" s="130"/>
+      <c r="S51" s="130"/>
+      <c r="T51" s="130"/>
+      <c r="U51" s="130"/>
+      <c r="V51" s="130"/>
+      <c r="W51" s="130"/>
+      <c r="X51" s="130"/>
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="B52" s="58" t="s">
@@ -4932,27 +4988,27 @@
       <c r="O52" s="58"/>
       <c r="P52" s="58"/>
       <c r="Q52" s="58"/>
-      <c r="R52" s="163"/>
-      <c r="S52" s="163"/>
-      <c r="T52" s="163"/>
-      <c r="U52" s="163"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="164"/>
+      <c r="T52" s="164"/>
+      <c r="U52" s="164"/>
       <c r="V52" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="W52" s="134"/>
-      <c r="X52" s="130"/>
-      <c r="Y52" s="130"/>
-      <c r="Z52" s="131"/>
-      <c r="AA52" s="134"/>
-      <c r="AB52" s="133"/>
+      <c r="W52" s="135"/>
+      <c r="X52" s="131"/>
+      <c r="Y52" s="131"/>
+      <c r="Z52" s="132"/>
+      <c r="AA52" s="135"/>
+      <c r="AB52" s="134"/>
       <c r="AC52" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="AD52" s="111"/>
-      <c r="AE52" s="112"/>
-      <c r="AF52" s="112"/>
-      <c r="AG52" s="112"/>
-      <c r="AH52" s="113"/>
+      <c r="AD52" s="112"/>
+      <c r="AE52" s="113"/>
+      <c r="AF52" s="113"/>
+      <c r="AG52" s="113"/>
+      <c r="AH52" s="114"/>
     </row>
     <row r="53" spans="1:35" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="58"/>
@@ -4990,73 +5046,73 @@
       <c r="AH53" s="83"/>
     </row>
     <row r="54" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="160" t="s">
+      <c r="B54" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="161"/>
-      <c r="D54" s="161"/>
-      <c r="E54" s="161"/>
-      <c r="F54" s="161"/>
-      <c r="G54" s="161"/>
-      <c r="H54" s="161"/>
-      <c r="I54" s="161"/>
-      <c r="J54" s="161"/>
-      <c r="K54" s="161"/>
+      <c r="C54" s="162"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="162"/>
+      <c r="K54" s="162"/>
       <c r="L54" s="59"/>
       <c r="M54" s="59"/>
       <c r="N54" s="59"/>
       <c r="O54" s="59"/>
       <c r="P54" s="59"/>
       <c r="Q54" s="59"/>
-      <c r="R54" s="126" t="s">
+      <c r="R54" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="S54" s="126"/>
-      <c r="T54" s="126"/>
-      <c r="U54" s="126"/>
+      <c r="S54" s="127"/>
+      <c r="T54" s="127"/>
+      <c r="U54" s="127"/>
       <c r="V54" s="59"/>
-      <c r="W54" s="126" t="s">
+      <c r="W54" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="X54" s="126"/>
-      <c r="Y54" s="126" t="s">
+      <c r="X54" s="127"/>
+      <c r="Y54" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Z54" s="126"/>
-      <c r="AA54" s="126" t="s">
+      <c r="Z54" s="127"/>
+      <c r="AA54" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="AB54" s="126"/>
+      <c r="AB54" s="127"/>
       <c r="AC54" s="59"/>
-      <c r="AD54" s="126" t="s">
+      <c r="AD54" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="AE54" s="126"/>
-      <c r="AF54" s="126"/>
-      <c r="AG54" s="126"/>
-      <c r="AH54" s="126"/>
+      <c r="AE54" s="127"/>
+      <c r="AF54" s="127"/>
+      <c r="AG54" s="127"/>
+      <c r="AH54" s="127"/>
     </row>
     <row r="55" spans="1:35" ht="9.1999999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="162"/>
-      <c r="C55" s="162"/>
-      <c r="D55" s="162"/>
-      <c r="E55" s="162"/>
-      <c r="F55" s="162"/>
-      <c r="G55" s="162"/>
-      <c r="H55" s="162"/>
-      <c r="I55" s="162"/>
-      <c r="J55" s="162"/>
-      <c r="K55" s="162"/>
-      <c r="L55" s="162"/>
-      <c r="M55" s="162"/>
-      <c r="N55" s="162"/>
-      <c r="O55" s="162"/>
-      <c r="P55" s="162"/>
+      <c r="B55" s="163"/>
+      <c r="C55" s="163"/>
+      <c r="D55" s="163"/>
+      <c r="E55" s="163"/>
+      <c r="F55" s="163"/>
+      <c r="G55" s="163"/>
+      <c r="H55" s="163"/>
+      <c r="I55" s="163"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="163"/>
+      <c r="L55" s="163"/>
+      <c r="M55" s="163"/>
+      <c r="N55" s="163"/>
+      <c r="O55" s="163"/>
+      <c r="P55" s="163"/>
       <c r="Q55" s="60"/>
-      <c r="R55" s="126"/>
-      <c r="S55" s="126"/>
-      <c r="T55" s="126"/>
-      <c r="U55" s="126"/>
+      <c r="R55" s="127"/>
+      <c r="S55" s="127"/>
+      <c r="T55" s="127"/>
+      <c r="U55" s="127"/>
       <c r="V55" s="59"/>
       <c r="W55" s="59"/>
       <c r="X55" s="54"/>
@@ -5065,19 +5121,19 @@
       <c r="AA55" s="54"/>
       <c r="AB55" s="54"/>
       <c r="AC55" s="61"/>
-      <c r="AD55" s="126"/>
-      <c r="AE55" s="126"/>
-      <c r="AF55" s="126"/>
-      <c r="AG55" s="126"/>
-      <c r="AH55" s="126"/>
+      <c r="AD55" s="127"/>
+      <c r="AE55" s="127"/>
+      <c r="AF55" s="127"/>
+      <c r="AG55" s="127"/>
+      <c r="AH55" s="127"/>
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" s="62"/>
-      <c r="B56" s="122" t="s">
+      <c r="B56" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="122"/>
-      <c r="D56" s="122"/>
+      <c r="C56" s="123"/>
+      <c r="D56" s="123"/>
       <c r="E56" s="77">
         <v>8</v>
       </c>
@@ -5104,71 +5160,71 @@
       <c r="R56" s="74"/>
       <c r="S56" s="74"/>
       <c r="T56" s="55"/>
-      <c r="V56" s="165" t="s">
+      <c r="V56" s="166" t="s">
         <v>51</v>
       </c>
-      <c r="W56" s="166"/>
-      <c r="X56" s="166"/>
-      <c r="Y56" s="166"/>
-      <c r="Z56" s="166"/>
-      <c r="AA56" s="166"/>
-      <c r="AB56" s="166"/>
-      <c r="AC56" s="166"/>
-      <c r="AD56" s="166"/>
-      <c r="AE56" s="166"/>
-      <c r="AF56" s="166"/>
-      <c r="AG56" s="166"/>
-      <c r="AH56" s="166"/>
-      <c r="AI56" s="167"/>
+      <c r="W56" s="167"/>
+      <c r="X56" s="167"/>
+      <c r="Y56" s="167"/>
+      <c r="Z56" s="167"/>
+      <c r="AA56" s="167"/>
+      <c r="AB56" s="167"/>
+      <c r="AC56" s="167"/>
+      <c r="AD56" s="167"/>
+      <c r="AE56" s="167"/>
+      <c r="AF56" s="167"/>
+      <c r="AG56" s="167"/>
+      <c r="AH56" s="167"/>
+      <c r="AI56" s="168"/>
     </row>
     <row r="57" spans="1:35" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F57" s="54"/>
-      <c r="G57" s="129" t="s">
+      <c r="G57" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="H57" s="129"/>
-      <c r="I57" s="129"/>
-      <c r="K57" s="129" t="s">
+      <c r="H57" s="130"/>
+      <c r="I57" s="130"/>
+      <c r="K57" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="L57" s="129"/>
-      <c r="M57" s="129"/>
-      <c r="N57" s="129"/>
-      <c r="O57" s="129"/>
-      <c r="P57" s="129"/>
-      <c r="Q57" s="129"/>
-      <c r="R57" s="129"/>
-      <c r="S57" s="129"/>
+      <c r="L57" s="130"/>
+      <c r="M57" s="130"/>
+      <c r="N57" s="130"/>
+      <c r="O57" s="130"/>
+      <c r="P57" s="130"/>
+      <c r="Q57" s="130"/>
+      <c r="R57" s="130"/>
+      <c r="S57" s="130"/>
       <c r="T57" s="53"/>
-      <c r="V57" s="168"/>
-      <c r="W57" s="169"/>
-      <c r="X57" s="169"/>
-      <c r="Y57" s="169"/>
-      <c r="Z57" s="169"/>
-      <c r="AA57" s="169"/>
-      <c r="AB57" s="169"/>
-      <c r="AC57" s="169"/>
-      <c r="AD57" s="169"/>
-      <c r="AE57" s="169"/>
-      <c r="AF57" s="169"/>
-      <c r="AG57" s="169"/>
-      <c r="AH57" s="169"/>
-      <c r="AI57" s="170"/>
+      <c r="V57" s="169"/>
+      <c r="W57" s="170"/>
+      <c r="X57" s="170"/>
+      <c r="Y57" s="170"/>
+      <c r="Z57" s="170"/>
+      <c r="AA57" s="170"/>
+      <c r="AB57" s="170"/>
+      <c r="AC57" s="170"/>
+      <c r="AD57" s="170"/>
+      <c r="AE57" s="170"/>
+      <c r="AF57" s="170"/>
+      <c r="AG57" s="170"/>
+      <c r="AH57" s="170"/>
+      <c r="AI57" s="171"/>
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" s="64"/>
-      <c r="B58" s="177"/>
-      <c r="C58" s="178"/>
-      <c r="D58" s="178"/>
-      <c r="E58" s="178"/>
-      <c r="F58" s="178"/>
-      <c r="G58" s="178"/>
-      <c r="H58" s="178"/>
-      <c r="I58" s="178"/>
-      <c r="J58" s="178"/>
-      <c r="K58" s="178"/>
-      <c r="L58" s="178"/>
-      <c r="M58" s="179"/>
+      <c r="B58" s="178"/>
+      <c r="C58" s="179"/>
+      <c r="D58" s="179"/>
+      <c r="E58" s="179"/>
+      <c r="F58" s="179"/>
+      <c r="G58" s="179"/>
+      <c r="H58" s="179"/>
+      <c r="I58" s="179"/>
+      <c r="J58" s="179"/>
+      <c r="K58" s="179"/>
+      <c r="L58" s="179"/>
+      <c r="M58" s="180"/>
       <c r="N58" s="55"/>
       <c r="O58" s="55"/>
       <c r="P58" s="55"/>
@@ -5176,37 +5232,37 @@
       <c r="R58" s="55"/>
       <c r="S58" s="55"/>
       <c r="T58" s="55"/>
-      <c r="V58" s="168"/>
-      <c r="W58" s="169"/>
-      <c r="X58" s="169"/>
-      <c r="Y58" s="169"/>
-      <c r="Z58" s="169"/>
-      <c r="AA58" s="169"/>
-      <c r="AB58" s="169"/>
-      <c r="AC58" s="169"/>
-      <c r="AD58" s="169"/>
-      <c r="AE58" s="169"/>
-      <c r="AF58" s="169"/>
-      <c r="AG58" s="169"/>
-      <c r="AH58" s="169"/>
-      <c r="AI58" s="170"/>
+      <c r="V58" s="169"/>
+      <c r="W58" s="170"/>
+      <c r="X58" s="170"/>
+      <c r="Y58" s="170"/>
+      <c r="Z58" s="170"/>
+      <c r="AA58" s="170"/>
+      <c r="AB58" s="170"/>
+      <c r="AC58" s="170"/>
+      <c r="AD58" s="170"/>
+      <c r="AE58" s="170"/>
+      <c r="AF58" s="170"/>
+      <c r="AG58" s="170"/>
+      <c r="AH58" s="170"/>
+      <c r="AI58" s="171"/>
     </row>
     <row r="59" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="64"/>
-      <c r="B59" s="180" t="s">
+      <c r="B59" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="180"/>
-      <c r="D59" s="180"/>
-      <c r="E59" s="180"/>
-      <c r="F59" s="180"/>
-      <c r="G59" s="180"/>
-      <c r="H59" s="180"/>
-      <c r="I59" s="180"/>
-      <c r="J59" s="180"/>
-      <c r="K59" s="180"/>
-      <c r="L59" s="180"/>
-      <c r="M59" s="180"/>
+      <c r="C59" s="181"/>
+      <c r="D59" s="181"/>
+      <c r="E59" s="181"/>
+      <c r="F59" s="181"/>
+      <c r="G59" s="181"/>
+      <c r="H59" s="181"/>
+      <c r="I59" s="181"/>
+      <c r="J59" s="181"/>
+      <c r="K59" s="181"/>
+      <c r="L59" s="181"/>
+      <c r="M59" s="181"/>
       <c r="N59" s="53"/>
       <c r="O59" s="53"/>
       <c r="P59" s="53"/>
@@ -5214,35 +5270,35 @@
       <c r="R59" s="53"/>
       <c r="S59" s="53"/>
       <c r="T59" s="53"/>
-      <c r="V59" s="171"/>
-      <c r="W59" s="172"/>
-      <c r="X59" s="172"/>
-      <c r="Y59" s="172"/>
-      <c r="Z59" s="172"/>
-      <c r="AA59" s="172"/>
-      <c r="AB59" s="172"/>
-      <c r="AC59" s="172"/>
-      <c r="AD59" s="172"/>
-      <c r="AE59" s="172"/>
-      <c r="AF59" s="172"/>
-      <c r="AG59" s="172"/>
-      <c r="AH59" s="172"/>
-      <c r="AI59" s="173"/>
+      <c r="V59" s="172"/>
+      <c r="W59" s="173"/>
+      <c r="X59" s="173"/>
+      <c r="Y59" s="173"/>
+      <c r="Z59" s="173"/>
+      <c r="AA59" s="173"/>
+      <c r="AB59" s="173"/>
+      <c r="AC59" s="173"/>
+      <c r="AD59" s="173"/>
+      <c r="AE59" s="173"/>
+      <c r="AF59" s="173"/>
+      <c r="AG59" s="173"/>
+      <c r="AH59" s="173"/>
+      <c r="AI59" s="174"/>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" s="64"/>
-      <c r="B60" s="182"/>
-      <c r="C60" s="183"/>
-      <c r="D60" s="183"/>
-      <c r="E60" s="183"/>
-      <c r="F60" s="183"/>
-      <c r="G60" s="183"/>
-      <c r="H60" s="183"/>
-      <c r="I60" s="183"/>
-      <c r="J60" s="183"/>
-      <c r="K60" s="183"/>
-      <c r="L60" s="183"/>
-      <c r="M60" s="184"/>
+      <c r="B60" s="183"/>
+      <c r="C60" s="184"/>
+      <c r="D60" s="184"/>
+      <c r="E60" s="184"/>
+      <c r="F60" s="184"/>
+      <c r="G60" s="184"/>
+      <c r="H60" s="184"/>
+      <c r="I60" s="184"/>
+      <c r="J60" s="184"/>
+      <c r="K60" s="184"/>
+      <c r="L60" s="184"/>
+      <c r="M60" s="185"/>
       <c r="N60" s="53"/>
       <c r="O60" s="53"/>
       <c r="P60" s="53"/>
@@ -5267,19 +5323,19 @@
     </row>
     <row r="61" spans="1:35" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="64"/>
-      <c r="B61" s="185" t="s">
+      <c r="B61" s="186" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="186"/>
-      <c r="D61" s="186"/>
-      <c r="E61" s="186"/>
-      <c r="F61" s="186"/>
-      <c r="G61" s="186"/>
-      <c r="H61" s="186"/>
-      <c r="I61" s="186"/>
-      <c r="J61" s="186"/>
-      <c r="K61" s="186"/>
-      <c r="L61" s="186"/>
+      <c r="C61" s="187"/>
+      <c r="D61" s="187"/>
+      <c r="E61" s="187"/>
+      <c r="F61" s="187"/>
+      <c r="G61" s="187"/>
+      <c r="H61" s="187"/>
+      <c r="I61" s="187"/>
+      <c r="J61" s="187"/>
+      <c r="K61" s="187"/>
+      <c r="L61" s="187"/>
       <c r="M61" s="82"/>
       <c r="N61" s="53"/>
       <c r="O61" s="53"/>
@@ -5304,249 +5360,236 @@
       <c r="AI61" s="81"/>
     </row>
     <row r="62" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="175" t="s">
+      <c r="A62" s="176" t="s">
         <v>97</v>
       </c>
-      <c r="B62" s="175"/>
-      <c r="C62" s="175"/>
-      <c r="D62" s="175"/>
-      <c r="E62" s="175"/>
-      <c r="F62" s="175"/>
-      <c r="G62" s="175"/>
-      <c r="H62" s="175"/>
-      <c r="I62" s="175"/>
-      <c r="J62" s="175"/>
-      <c r="K62" s="175"/>
-      <c r="L62" s="175"/>
-      <c r="M62" s="175"/>
-      <c r="N62" s="175"/>
-      <c r="O62" s="175"/>
-      <c r="P62" s="175"/>
-      <c r="Q62" s="175"/>
-      <c r="R62" s="175"/>
-      <c r="S62" s="175"/>
-      <c r="T62" s="175"/>
-      <c r="U62" s="175"/>
-      <c r="V62" s="175"/>
-      <c r="W62" s="175"/>
-      <c r="X62" s="175"/>
-      <c r="Y62" s="175"/>
-      <c r="Z62" s="175"/>
-      <c r="AA62" s="175"/>
-      <c r="AB62" s="175"/>
-      <c r="AC62" s="175"/>
-      <c r="AD62" s="175"/>
-      <c r="AE62" s="175"/>
-      <c r="AF62" s="175"/>
-      <c r="AG62" s="175"/>
-      <c r="AH62" s="175"/>
-      <c r="AI62" s="175"/>
+      <c r="B62" s="176"/>
+      <c r="C62" s="176"/>
+      <c r="D62" s="176"/>
+      <c r="E62" s="176"/>
+      <c r="F62" s="176"/>
+      <c r="G62" s="176"/>
+      <c r="H62" s="176"/>
+      <c r="I62" s="176"/>
+      <c r="J62" s="176"/>
+      <c r="K62" s="176"/>
+      <c r="L62" s="176"/>
+      <c r="M62" s="176"/>
+      <c r="N62" s="176"/>
+      <c r="O62" s="176"/>
+      <c r="P62" s="176"/>
+      <c r="Q62" s="176"/>
+      <c r="R62" s="176"/>
+      <c r="S62" s="176"/>
+      <c r="T62" s="176"/>
+      <c r="U62" s="176"/>
+      <c r="V62" s="176"/>
+      <c r="W62" s="176"/>
+      <c r="X62" s="176"/>
+      <c r="Y62" s="176"/>
+      <c r="Z62" s="176"/>
+      <c r="AA62" s="176"/>
+      <c r="AB62" s="176"/>
+      <c r="AC62" s="176"/>
+      <c r="AD62" s="176"/>
+      <c r="AE62" s="176"/>
+      <c r="AF62" s="176"/>
+      <c r="AG62" s="176"/>
+      <c r="AH62" s="176"/>
+      <c r="AI62" s="176"/>
     </row>
     <row r="63" spans="1:35" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="176"/>
-      <c r="B63" s="176"/>
-      <c r="C63" s="176"/>
-      <c r="D63" s="176"/>
-      <c r="E63" s="176"/>
-      <c r="F63" s="176"/>
-      <c r="G63" s="176"/>
-      <c r="H63" s="176"/>
-      <c r="I63" s="176"/>
-      <c r="J63" s="176"/>
-      <c r="K63" s="176"/>
-      <c r="L63" s="176"/>
-      <c r="M63" s="176"/>
-      <c r="N63" s="176"/>
-      <c r="O63" s="176"/>
-      <c r="P63" s="176"/>
-      <c r="Q63" s="176"/>
-      <c r="R63" s="176"/>
-      <c r="S63" s="176"/>
-      <c r="T63" s="176"/>
-      <c r="U63" s="176"/>
-      <c r="V63" s="176"/>
-      <c r="W63" s="176"/>
-      <c r="X63" s="176"/>
-      <c r="Y63" s="176"/>
-      <c r="Z63" s="176"/>
-      <c r="AA63" s="176"/>
-      <c r="AB63" s="176"/>
-      <c r="AC63" s="176"/>
-      <c r="AD63" s="176"/>
-      <c r="AE63" s="176"/>
-      <c r="AF63" s="176"/>
-      <c r="AG63" s="176"/>
-      <c r="AH63" s="176"/>
-      <c r="AI63" s="176"/>
+      <c r="A63" s="177"/>
+      <c r="B63" s="177"/>
+      <c r="C63" s="177"/>
+      <c r="D63" s="177"/>
+      <c r="E63" s="177"/>
+      <c r="F63" s="177"/>
+      <c r="G63" s="177"/>
+      <c r="H63" s="177"/>
+      <c r="I63" s="177"/>
+      <c r="J63" s="177"/>
+      <c r="K63" s="177"/>
+      <c r="L63" s="177"/>
+      <c r="M63" s="177"/>
+      <c r="N63" s="177"/>
+      <c r="O63" s="177"/>
+      <c r="P63" s="177"/>
+      <c r="Q63" s="177"/>
+      <c r="R63" s="177"/>
+      <c r="S63" s="177"/>
+      <c r="T63" s="177"/>
+      <c r="U63" s="177"/>
+      <c r="V63" s="177"/>
+      <c r="W63" s="177"/>
+      <c r="X63" s="177"/>
+      <c r="Y63" s="177"/>
+      <c r="Z63" s="177"/>
+      <c r="AA63" s="177"/>
+      <c r="AB63" s="177"/>
+      <c r="AC63" s="177"/>
+      <c r="AD63" s="177"/>
+      <c r="AE63" s="177"/>
+      <c r="AF63" s="177"/>
+      <c r="AG63" s="177"/>
+      <c r="AH63" s="177"/>
+      <c r="AI63" s="177"/>
     </row>
     <row r="64" spans="1:35" ht="12.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="181" t="s">
+      <c r="A64" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="B64" s="181"/>
-      <c r="C64" s="181"/>
-      <c r="D64" s="181"/>
-      <c r="E64" s="181"/>
-      <c r="F64" s="181"/>
-      <c r="G64" s="181"/>
-      <c r="H64" s="181"/>
-      <c r="I64" s="181"/>
-      <c r="J64" s="181"/>
-      <c r="K64" s="181"/>
-      <c r="L64" s="181"/>
-      <c r="M64" s="181"/>
-      <c r="N64" s="181"/>
-      <c r="O64" s="181"/>
-      <c r="P64" s="181"/>
-      <c r="Q64" s="181"/>
-      <c r="R64" s="181"/>
-      <c r="S64" s="181"/>
-      <c r="T64" s="181"/>
-      <c r="U64" s="181"/>
-      <c r="V64" s="181"/>
-      <c r="W64" s="181"/>
-      <c r="X64" s="181"/>
-      <c r="Y64" s="181"/>
-      <c r="Z64" s="181"/>
-      <c r="AA64" s="181"/>
-      <c r="AB64" s="181"/>
-      <c r="AC64" s="181"/>
-      <c r="AD64" s="181"/>
-      <c r="AE64" s="181"/>
-      <c r="AF64" s="181"/>
-      <c r="AG64" s="181"/>
-      <c r="AH64" s="181"/>
-      <c r="AI64" s="181"/>
+      <c r="B64" s="182"/>
+      <c r="C64" s="182"/>
+      <c r="D64" s="182"/>
+      <c r="E64" s="182"/>
+      <c r="F64" s="182"/>
+      <c r="G64" s="182"/>
+      <c r="H64" s="182"/>
+      <c r="I64" s="182"/>
+      <c r="J64" s="182"/>
+      <c r="K64" s="182"/>
+      <c r="L64" s="182"/>
+      <c r="M64" s="182"/>
+      <c r="N64" s="182"/>
+      <c r="O64" s="182"/>
+      <c r="P64" s="182"/>
+      <c r="Q64" s="182"/>
+      <c r="R64" s="182"/>
+      <c r="S64" s="182"/>
+      <c r="T64" s="182"/>
+      <c r="U64" s="182"/>
+      <c r="V64" s="182"/>
+      <c r="W64" s="182"/>
+      <c r="X64" s="182"/>
+      <c r="Y64" s="182"/>
+      <c r="Z64" s="182"/>
+      <c r="AA64" s="182"/>
+      <c r="AB64" s="182"/>
+      <c r="AC64" s="182"/>
+      <c r="AD64" s="182"/>
+      <c r="AE64" s="182"/>
+      <c r="AF64" s="182"/>
+      <c r="AG64" s="182"/>
+      <c r="AH64" s="182"/>
+      <c r="AI64" s="182"/>
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A65" s="174" t="s">
+      <c r="A65" s="175" t="s">
         <v>58</v>
       </c>
-      <c r="B65" s="174"/>
-      <c r="C65" s="174"/>
-      <c r="D65" s="174"/>
-      <c r="E65" s="174"/>
-      <c r="F65" s="174"/>
-      <c r="G65" s="174"/>
-      <c r="H65" s="174"/>
-      <c r="I65" s="174"/>
-      <c r="J65" s="174"/>
-      <c r="K65" s="174"/>
-      <c r="L65" s="174"/>
-      <c r="M65" s="174"/>
-      <c r="N65" s="174"/>
-      <c r="O65" s="174"/>
-      <c r="P65" s="174"/>
-      <c r="Q65" s="174"/>
-      <c r="R65" s="174"/>
-      <c r="S65" s="174"/>
-      <c r="T65" s="174"/>
-      <c r="U65" s="174"/>
-      <c r="V65" s="174"/>
-      <c r="W65" s="174"/>
-      <c r="X65" s="174"/>
-      <c r="Y65" s="174"/>
-      <c r="Z65" s="174"/>
-      <c r="AA65" s="174"/>
-      <c r="AB65" s="174"/>
-      <c r="AC65" s="174"/>
-      <c r="AD65" s="174"/>
-      <c r="AE65" s="174"/>
-      <c r="AF65" s="174"/>
-      <c r="AG65" s="174"/>
-      <c r="AH65" s="174"/>
-      <c r="AI65" s="174"/>
+      <c r="B65" s="175"/>
+      <c r="C65" s="175"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="175"/>
+      <c r="F65" s="175"/>
+      <c r="G65" s="175"/>
+      <c r="H65" s="175"/>
+      <c r="I65" s="175"/>
+      <c r="J65" s="175"/>
+      <c r="K65" s="175"/>
+      <c r="L65" s="175"/>
+      <c r="M65" s="175"/>
+      <c r="N65" s="175"/>
+      <c r="O65" s="175"/>
+      <c r="P65" s="175"/>
+      <c r="Q65" s="175"/>
+      <c r="R65" s="175"/>
+      <c r="S65" s="175"/>
+      <c r="T65" s="175"/>
+      <c r="U65" s="175"/>
+      <c r="V65" s="175"/>
+      <c r="W65" s="175"/>
+      <c r="X65" s="175"/>
+      <c r="Y65" s="175"/>
+      <c r="Z65" s="175"/>
+      <c r="AA65" s="175"/>
+      <c r="AB65" s="175"/>
+      <c r="AC65" s="175"/>
+      <c r="AD65" s="175"/>
+      <c r="AE65" s="175"/>
+      <c r="AF65" s="175"/>
+      <c r="AG65" s="175"/>
+      <c r="AH65" s="175"/>
+      <c r="AI65" s="175"/>
     </row>
     <row r="71" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="C71" s="164"/>
-      <c r="D71" s="164"/>
-      <c r="E71" s="164"/>
-      <c r="F71" s="164"/>
-      <c r="G71" s="164"/>
-      <c r="H71" s="164"/>
-      <c r="I71" s="164"/>
-      <c r="J71" s="164"/>
-      <c r="K71" s="164"/>
-      <c r="L71" s="164"/>
-      <c r="M71" s="164"/>
-      <c r="N71" s="164"/>
-      <c r="O71" s="164"/>
-      <c r="P71" s="164"/>
-      <c r="Q71" s="164"/>
-      <c r="R71" s="164"/>
-      <c r="S71" s="164"/>
-      <c r="T71" s="164"/>
-      <c r="U71" s="164"/>
-      <c r="V71" s="164"/>
-      <c r="W71" s="164"/>
-      <c r="X71" s="164"/>
-      <c r="Y71" s="164"/>
-      <c r="Z71" s="164"/>
-      <c r="AA71" s="164"/>
-      <c r="AB71" s="164"/>
-      <c r="AC71" s="164"/>
-      <c r="AD71" s="164"/>
-      <c r="AE71" s="164"/>
-      <c r="AF71" s="164"/>
-      <c r="AG71" s="164"/>
-      <c r="AH71" s="164"/>
-      <c r="AI71" s="164"/>
-      <c r="AJ71" s="164"/>
-      <c r="AK71" s="164"/>
+      <c r="C71" s="165"/>
+      <c r="D71" s="165"/>
+      <c r="E71" s="165"/>
+      <c r="F71" s="165"/>
+      <c r="G71" s="165"/>
+      <c r="H71" s="165"/>
+      <c r="I71" s="165"/>
+      <c r="J71" s="165"/>
+      <c r="K71" s="165"/>
+      <c r="L71" s="165"/>
+      <c r="M71" s="165"/>
+      <c r="N71" s="165"/>
+      <c r="O71" s="165"/>
+      <c r="P71" s="165"/>
+      <c r="Q71" s="165"/>
+      <c r="R71" s="165"/>
+      <c r="S71" s="165"/>
+      <c r="T71" s="165"/>
+      <c r="U71" s="165"/>
+      <c r="V71" s="165"/>
+      <c r="W71" s="165"/>
+      <c r="X71" s="165"/>
+      <c r="Y71" s="165"/>
+      <c r="Z71" s="165"/>
+      <c r="AA71" s="165"/>
+      <c r="AB71" s="165"/>
+      <c r="AC71" s="165"/>
+      <c r="AD71" s="165"/>
+      <c r="AE71" s="165"/>
+      <c r="AF71" s="165"/>
+      <c r="AG71" s="165"/>
+      <c r="AH71" s="165"/>
+      <c r="AI71" s="165"/>
+      <c r="AJ71" s="165"/>
+      <c r="AK71" s="165"/>
     </row>
     <row r="72" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="C72" s="164"/>
-      <c r="D72" s="164"/>
-      <c r="E72" s="164"/>
-      <c r="F72" s="164"/>
-      <c r="G72" s="164"/>
-      <c r="H72" s="164"/>
-      <c r="I72" s="164"/>
-      <c r="J72" s="164"/>
-      <c r="K72" s="164"/>
-      <c r="L72" s="164"/>
-      <c r="M72" s="164"/>
-      <c r="N72" s="164"/>
-      <c r="O72" s="164"/>
-      <c r="P72" s="164"/>
-      <c r="Q72" s="164"/>
-      <c r="R72" s="164"/>
-      <c r="S72" s="164"/>
-      <c r="T72" s="164"/>
-      <c r="U72" s="164"/>
-      <c r="V72" s="164"/>
-      <c r="W72" s="164"/>
-      <c r="X72" s="164"/>
-      <c r="Y72" s="164"/>
-      <c r="Z72" s="164"/>
-      <c r="AA72" s="164"/>
-      <c r="AB72" s="164"/>
-      <c r="AC72" s="164"/>
-      <c r="AD72" s="164"/>
-      <c r="AE72" s="164"/>
-      <c r="AF72" s="164"/>
-      <c r="AG72" s="164"/>
-      <c r="AH72" s="164"/>
-      <c r="AI72" s="164"/>
-      <c r="AJ72" s="164"/>
-      <c r="AK72" s="164"/>
+      <c r="C72" s="165"/>
+      <c r="D72" s="165"/>
+      <c r="E72" s="165"/>
+      <c r="F72" s="165"/>
+      <c r="G72" s="165"/>
+      <c r="H72" s="165"/>
+      <c r="I72" s="165"/>
+      <c r="J72" s="165"/>
+      <c r="K72" s="165"/>
+      <c r="L72" s="165"/>
+      <c r="M72" s="165"/>
+      <c r="N72" s="165"/>
+      <c r="O72" s="165"/>
+      <c r="P72" s="165"/>
+      <c r="Q72" s="165"/>
+      <c r="R72" s="165"/>
+      <c r="S72" s="165"/>
+      <c r="T72" s="165"/>
+      <c r="U72" s="165"/>
+      <c r="V72" s="165"/>
+      <c r="W72" s="165"/>
+      <c r="X72" s="165"/>
+      <c r="Y72" s="165"/>
+      <c r="Z72" s="165"/>
+      <c r="AA72" s="165"/>
+      <c r="AB72" s="165"/>
+      <c r="AC72" s="165"/>
+      <c r="AD72" s="165"/>
+      <c r="AE72" s="165"/>
+      <c r="AF72" s="165"/>
+      <c r="AG72" s="165"/>
+      <c r="AH72" s="165"/>
+      <c r="AI72" s="165"/>
+      <c r="AJ72" s="165"/>
+      <c r="AK72" s="165"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <protectedRanges>
-    <protectedRange sqref="V56 A59:A61 N59:T61 U56:U61 W56:AI61 V58:V61 C71:AK72 A43 L43:AJ44 A64:AI64 B44:B46 G43:H43 E43 C43:D46 E44:H44 AD45:AJ46" name="Диапазон7"/>
-    <protectedRange sqref="B56 B41:D42 E41:F41 J41 F42:S42 A51:A61 B57:C57 D56:D57 E56:F56 J56 F57:T57 AI52:AI55 Z51:AI51 M51:X51" name="Диапазон6"/>
-    <protectedRange sqref="A47:P47 Y47:AI47 Y48:Y50 Z50 A48:A49 A50:B50 P48:P50 Q47:X50" name="Диапазон5"/>
-    <protectedRange sqref="A1" name="Диапазон2"/>
-    <protectedRange sqref="A1 A38:E39 F39 AI38 A40:H40 W24:AB25 AG9 AG38 P11:AI11 A10:N11 A9:I9 A16:B17 AI14:AI17 A14:L14 U18:AH18 S18 B18:L18 N18:Q18 A19 A23:A24 N24:O24 J24:L24 C24:I25 A25:B25 AB14:AH14 Z14 N14:S14 U14:X14 W12:AB13 N12:O12 J12:L12 A13:B13 A28:B29 AI26:AI29 A26:L26 U30:AH30 S30 B30:L30 N30:Q30 A31 A36 AB26:AH26 Z26 N26:S26 U26:X26 A41:A42 A44:A46 A12 C12:I13 A15:AH15 A27:AH27" name="Диапазон1"/>
-    <protectedRange sqref="C17 G17 K17 O17 S17 W17 AA17 AE17 AA29 AE29 C29 G29 K29 O29 S29 W29" name="Диапазон4_1"/>
-    <protectedRange sqref="B52:B53 R54:U54 C55:Q55 X55:Y55 W54:AB54 AD54:AH55 D52:Q53 AD25:AI25 Q13:V13 AD13:AI13 Q25:V25" name="Диапазон2_4"/>
-    <protectedRange sqref="R52:V53 AC24 R12 P12 AC12 P24 AE12 Y45 X52:X53 AE24 R24" name="Диапазон5_4"/>
-    <protectedRange sqref="A62:AI63" name="Диапазон7_3"/>
-    <protectedRange sqref="E45:I46 J46 L45 V45:W45 N46:W46" name="Диапазон7_2"/>
-    <protectedRange sqref="X46:AC46" name="Диапазон2_4_2"/>
-  </protectedRanges>
-  <mergeCells count="215">
+  <sheetProtection algorithmName="SHA-512" hashValue="6VQ7bJj2GF4v1I5Ef474nIrtnQ6amJSZ92P7tXPECY5NqVhokbxaPw+5pBvj76U8+sdL2IduYus+F6lzhIy1Sg==" saltValue="P1MW9CpKOZLwAmST/hqtSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
+  <mergeCells count="216">
     <mergeCell ref="A43:D44"/>
     <mergeCell ref="E43:AI43"/>
     <mergeCell ref="E44:AI44"/>
@@ -5559,7 +5602,6 @@
     <mergeCell ref="J46:W46"/>
     <mergeCell ref="Z45:AA45"/>
     <mergeCell ref="AB45:AC45"/>
-    <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="M29:N29"/>
@@ -5582,7 +5624,6 @@
     <mergeCell ref="AG29:AH29"/>
     <mergeCell ref="AC26:AF26"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="Q48:X50"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="Y26:Z26"/>
     <mergeCell ref="AD24:AE24"/>
@@ -5606,6 +5647,7 @@
     <mergeCell ref="S24:T24"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C16:J16"/>
     <mergeCell ref="K16:R16"/>
     <mergeCell ref="S16:Z16"/>
@@ -5630,6 +5672,7 @@
     <mergeCell ref="AF22:AH22"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="A22:U22"/>
+    <mergeCell ref="B48:O49"/>
     <mergeCell ref="C71:AK72"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="V56:AI59"/>
@@ -5642,6 +5685,8 @@
     <mergeCell ref="A64:AI64"/>
     <mergeCell ref="B60:M60"/>
     <mergeCell ref="B61:L61"/>
+    <mergeCell ref="Q48:X50"/>
+    <mergeCell ref="M31:U31"/>
     <mergeCell ref="AD52:AH52"/>
     <mergeCell ref="S26:X26"/>
     <mergeCell ref="J39:V39"/>
@@ -5665,7 +5710,7 @@
     <mergeCell ref="Y54:Z54"/>
     <mergeCell ref="AA54:AB54"/>
     <mergeCell ref="C27:J27"/>
-    <mergeCell ref="B48:O49"/>
+    <mergeCell ref="J13:O13"/>
     <mergeCell ref="W22:X22"/>
     <mergeCell ref="Z22:AA22"/>
     <mergeCell ref="F26:J26"/>
@@ -5689,7 +5734,7 @@
     <mergeCell ref="A32:U32"/>
     <mergeCell ref="W29:X29"/>
     <mergeCell ref="B31:L31"/>
-    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="J12:L12"/>
     <mergeCell ref="AF20:AH20"/>
     <mergeCell ref="M19:U19"/>
     <mergeCell ref="W19:X19"/>
@@ -5713,7 +5758,7 @@
     <mergeCell ref="K15:R15"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="AH13:AI13"/>
-    <mergeCell ref="J13:O13"/>
+    <mergeCell ref="Q17:R17"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="B10:L10"/>
@@ -5737,7 +5782,7 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="X12:Z12"/>
     <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="W39:X39"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A2:AI3"/>
     <mergeCell ref="W5:X5"/>
@@ -5761,38 +5806,34 @@
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="Y17:Z17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="Q17:R17"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R52:U53">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R52:U53" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$AN$6:$AN$8</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y5:AH5 D7:P7 S7:AA7 Y38:AH38 E41 G41:I41 K41:M41 O41:P41 R41:S41 E56 G56:I56 K56:M56 O56:P56 R56:S56">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y5:AH5 D7:P7 S7:AA7 Y38:AH39 E41 G41:I41 K41:M41 O41:P41 R41:S41 E56 G56:I56 K56:M56 O56:P56 R56:S56" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M10:AH10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M10:AH10" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$AK$6:$AK$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q12:R12 AD24:AE24 AD12:AE12 W52:X53 X45:Y45 Q24:R24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q12:R12 AD24:AE24 AD12:AE12 W52:X53 X45:Y45 Q24:R24" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>$AP$6:$AP$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S12:T12 AF24:AG24 AF12:AG12 Y52:Z53 Z45:AA45 S24:T24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S12:T12 AF24:AG24 AF12:AG12 Y52:Z53 Z45:AA45 S24:T24" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>$AQ$6:$AQ$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG14:AH14 AG26:AH26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG14:AH14 AG26:AH26" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$AM$6:$AM$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:O12 N24:O24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N12:O12 N24:O24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>$AK$17:$AK$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA53:AB53">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA53:AB53" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>$AR$6:$AR$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA52:AB52">
-      <formula1>$AR$6:$AR$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U12:V12 AH12:AI12 U24:V24 AH24:AI24 AB45:AC45">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA52:AB52 U12:V12 AH12:AI12 U24:V24 AH24:AI24 AB45:AC45" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>$AR$6:$AR$37</formula1>
     </dataValidation>
   </dataValidations>
